--- a/research/traditional_assets/database/data/canada/canada_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_retail_building_supply.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08706475818401804</v>
+        <v>0.08686711157483039</v>
       </c>
       <c r="C2">
-        <v>1434.439799832892</v>
+        <v>1424.560608589763</v>
       </c>
       <c r="D2">
-        <v>1341.839799832892</v>
+        <v>1347.246608589763</v>
       </c>
       <c r="E2">
-        <v>-306.8</v>
+        <v>-291.514</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.286</v>
       </c>
       <c r="G2">
         <v>92.59999999999999</v>
@@ -1707,28 +1707,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7688858</v>
       </c>
       <c r="N2">
-        <v>41.59999999999999</v>
+        <v>40.83111419999999</v>
       </c>
       <c r="O2">
-        <v>11.024</v>
+        <v>10.820245263</v>
       </c>
       <c r="P2">
-        <v>30.57599999999999</v>
+        <v>30.010868937</v>
       </c>
       <c r="Q2">
-        <v>109.776</v>
+        <v>109.210868937</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08706475818401804</v>
+        <v>0.08737111775235393</v>
       </c>
       <c r="T2">
-        <v>0.952996724804112</v>
+        <v>0.9600720035185667</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>54.10426359805318</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08686711157483039</v>
+        <v>0.08666946496564273</v>
       </c>
       <c r="C3">
-        <v>1424.560608589763</v>
+        <v>1414.725166013613</v>
       </c>
       <c r="D3">
-        <v>1347.246608589763</v>
+        <v>1352.697166013613</v>
       </c>
       <c r="E3">
-        <v>-291.514</v>
+        <v>-276.228</v>
       </c>
       <c r="F3">
-        <v>15.286</v>
+        <v>30.572</v>
       </c>
       <c r="G3">
         <v>92.59999999999999</v>
@@ -1789,28 +1789,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M3">
-        <v>0.7688858</v>
+        <v>1.5377716</v>
       </c>
       <c r="N3">
-        <v>40.83111419999999</v>
+        <v>40.0622284</v>
       </c>
       <c r="O3">
-        <v>10.820245263</v>
+        <v>10.616490526</v>
       </c>
       <c r="P3">
-        <v>30.010868937</v>
+        <v>29.445737874</v>
       </c>
       <c r="Q3">
-        <v>109.210868937</v>
+        <v>108.645737874</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08737111775235393</v>
+        <v>0.08768372955677831</v>
       </c>
       <c r="T3">
-        <v>0.9600720035185667</v>
+        <v>0.9672916756761736</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>54.10426359805318</v>
+        <v>27.05213179902659</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08666946496564273</v>
+        <v>0.08647181835645509</v>
       </c>
       <c r="C4">
-        <v>1414.725166013613</v>
+        <v>1404.934005243487</v>
       </c>
       <c r="D4">
-        <v>1352.697166013613</v>
+        <v>1358.192005243487</v>
       </c>
       <c r="E4">
-        <v>-276.228</v>
+        <v>-260.942</v>
       </c>
       <c r="F4">
-        <v>30.572</v>
+        <v>45.858</v>
       </c>
       <c r="G4">
         <v>92.59999999999999</v>
@@ -1871,28 +1871,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M4">
-        <v>1.5377716</v>
+        <v>2.3066574</v>
       </c>
       <c r="N4">
-        <v>40.0622284</v>
+        <v>39.2933426</v>
       </c>
       <c r="O4">
-        <v>10.616490526</v>
+        <v>10.412735789</v>
       </c>
       <c r="P4">
-        <v>29.445737874</v>
+        <v>28.880606811</v>
       </c>
       <c r="Q4">
-        <v>108.645737874</v>
+        <v>108.080606811</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08768372955677831</v>
+        <v>0.08800278696541763</v>
       </c>
       <c r="T4">
-        <v>0.9672916756761736</v>
+        <v>0.9746602070535252</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>27.05213179902659</v>
+        <v>18.0347545326844</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08647181835645509</v>
+        <v>0.08627417174726745</v>
       </c>
       <c r="C5">
-        <v>1404.934005243487</v>
+        <v>1395.187668116494</v>
       </c>
       <c r="D5">
-        <v>1358.192005243487</v>
+        <v>1363.731668116495</v>
       </c>
       <c r="E5">
-        <v>-260.942</v>
+        <v>-245.656</v>
       </c>
       <c r="F5">
-        <v>45.858</v>
+        <v>61.144</v>
       </c>
       <c r="G5">
         <v>92.59999999999999</v>
@@ -1953,28 +1953,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M5">
-        <v>2.3066574</v>
+        <v>3.0755432</v>
       </c>
       <c r="N5">
-        <v>39.2933426</v>
+        <v>38.5244568</v>
       </c>
       <c r="O5">
-        <v>10.412735789</v>
+        <v>10.208981052</v>
       </c>
       <c r="P5">
-        <v>28.880606811</v>
+        <v>28.315475748</v>
       </c>
       <c r="Q5">
-        <v>108.080606811</v>
+        <v>107.515475748</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08800278696541763</v>
+        <v>0.0883284914034036</v>
       </c>
       <c r="T5">
-        <v>0.9746602070535252</v>
+        <v>0.9821822495012379</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>18.0347545326844</v>
+        <v>13.52606589951329</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08627417174726745</v>
+        <v>0.0861316501380798</v>
       </c>
       <c r="C6">
-        <v>1395.187668116494</v>
+        <v>1383.924405091781</v>
       </c>
       <c r="D6">
-        <v>1363.731668116495</v>
+        <v>1367.754405091781</v>
       </c>
       <c r="E6">
-        <v>-245.656</v>
+        <v>-230.37</v>
       </c>
       <c r="F6">
-        <v>61.144</v>
+        <v>76.42999999999999</v>
       </c>
       <c r="G6">
         <v>92.59999999999999</v>
@@ -2035,45 +2035,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M6">
-        <v>3.0755432</v>
+        <v>3.959073999999999</v>
       </c>
       <c r="N6">
-        <v>38.5244568</v>
+        <v>37.64092599999999</v>
       </c>
       <c r="O6">
-        <v>10.208981052</v>
+        <v>9.974845389999999</v>
       </c>
       <c r="P6">
-        <v>28.315475748</v>
+        <v>27.66608060999999</v>
       </c>
       <c r="Q6">
-        <v>107.515475748</v>
+        <v>106.86608061</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0883284914034036</v>
+        <v>0.08866105277692612</v>
       </c>
       <c r="T6">
-        <v>0.9821822495012379</v>
+        <v>0.9898626507373238</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.265</v>
       </c>
       <c r="W6">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.52606589951329</v>
+        <v>10.50750756363736</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0861316501380798</v>
+        <v>0.08601999852889215</v>
       </c>
       <c r="C7">
-        <v>1383.924405091781</v>
+        <v>1371.806439327914</v>
       </c>
       <c r="D7">
-        <v>1367.754405091781</v>
+        <v>1370.922439327914</v>
       </c>
       <c r="E7">
-        <v>-230.37</v>
+        <v>-215.084</v>
       </c>
       <c r="F7">
-        <v>76.42999999999999</v>
+        <v>91.71600000000001</v>
       </c>
       <c r="G7">
         <v>92.59999999999999</v>
@@ -2117,45 +2117,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M7">
-        <v>3.959073999999999</v>
+        <v>4.906806</v>
       </c>
       <c r="N7">
-        <v>37.64092599999999</v>
+        <v>36.69319399999999</v>
       </c>
       <c r="O7">
-        <v>9.974845389999999</v>
+        <v>9.723696409999999</v>
       </c>
       <c r="P7">
-        <v>27.66608060999999</v>
+        <v>26.96949758999999</v>
       </c>
       <c r="Q7">
-        <v>106.86608061</v>
+        <v>106.16949759</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08866105277692612</v>
+        <v>0.08900068992435337</v>
       </c>
       <c r="T7">
-        <v>0.9898626507373238</v>
+        <v>0.9977064647656667</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.265</v>
       </c>
       <c r="W7">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.50750756363736</v>
+        <v>8.478020121439485</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08601999852889215</v>
+        <v>0.08588703191970452</v>
       </c>
       <c r="C8">
-        <v>1371.806439327914</v>
+        <v>1360.312470119731</v>
       </c>
       <c r="D8">
-        <v>1370.922439327914</v>
+        <v>1374.714470119731</v>
       </c>
       <c r="E8">
-        <v>-215.084</v>
+        <v>-199.798</v>
       </c>
       <c r="F8">
-        <v>91.71599999999999</v>
+        <v>107.002</v>
       </c>
       <c r="G8">
         <v>92.59999999999999</v>
@@ -2199,45 +2199,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M8">
-        <v>4.906806</v>
+        <v>5.810208599999999</v>
       </c>
       <c r="N8">
-        <v>36.69319399999999</v>
+        <v>35.7897914</v>
       </c>
       <c r="O8">
-        <v>9.723696409999999</v>
+        <v>9.484294720999999</v>
       </c>
       <c r="P8">
-        <v>26.96949758999999</v>
+        <v>26.305496679</v>
       </c>
       <c r="Q8">
-        <v>106.16949759</v>
+        <v>105.505496679</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08900068992435337</v>
+        <v>0.08934763109645646</v>
       </c>
       <c r="T8">
-        <v>0.9977064647656665</v>
+        <v>1.005718962966662</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.265</v>
       </c>
       <c r="W8">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.478020121439485</v>
+        <v>7.159811783693963</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08588703191970451</v>
+        <v>0.08571878531051688</v>
       </c>
       <c r="C9">
-        <v>1360.312470119732</v>
+        <v>1349.854810501717</v>
       </c>
       <c r="D9">
-        <v>1374.714470119732</v>
+        <v>1379.542810501717</v>
       </c>
       <c r="E9">
-        <v>-199.798</v>
+        <v>-184.512</v>
       </c>
       <c r="F9">
-        <v>107.002</v>
+        <v>122.288</v>
       </c>
       <c r="G9">
         <v>92.59999999999999</v>
@@ -2281,28 +2281,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M9">
-        <v>5.810208600000001</v>
+        <v>6.6402384</v>
       </c>
       <c r="N9">
-        <v>35.78979139999999</v>
+        <v>34.95976159999999</v>
       </c>
       <c r="O9">
-        <v>9.484294720999998</v>
+        <v>9.264336823999999</v>
       </c>
       <c r="P9">
-        <v>26.30549667899999</v>
+        <v>25.695424776</v>
       </c>
       <c r="Q9">
-        <v>105.505496679</v>
+        <v>104.895424776</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08934763109645646</v>
+        <v>0.08970211446795312</v>
       </c>
       <c r="T9">
-        <v>1.005718962966662</v>
+        <v>1.013905645911158</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.15981178369396</v>
+        <v>6.264835310732216</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08571878531051688</v>
+        <v>0.08561668870132921</v>
       </c>
       <c r="C10">
-        <v>1349.854810501717</v>
+        <v>1337.515349322472</v>
       </c>
       <c r="D10">
-        <v>1379.542810501717</v>
+        <v>1382.489349322472</v>
       </c>
       <c r="E10">
-        <v>-184.512</v>
+        <v>-169.226</v>
       </c>
       <c r="F10">
-        <v>122.288</v>
+        <v>137.574</v>
       </c>
       <c r="G10">
         <v>92.59999999999999</v>
@@ -2363,45 +2363,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M10">
-        <v>6.6402384</v>
+        <v>7.607842199999999</v>
       </c>
       <c r="N10">
-        <v>34.95976159999999</v>
+        <v>33.99215779999999</v>
       </c>
       <c r="O10">
-        <v>9.264336823999999</v>
+        <v>9.007921817</v>
       </c>
       <c r="P10">
-        <v>25.695424776</v>
+        <v>24.98423598299999</v>
       </c>
       <c r="Q10">
-        <v>104.895424776</v>
+        <v>104.184235983</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08970211446795312</v>
+        <v>0.09006438868277936</v>
       </c>
       <c r="T10">
-        <v>1.013905645911158</v>
+        <v>1.022272255953334</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.265</v>
       </c>
       <c r="W10">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.264835310732216</v>
+        <v>5.468041910753616</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08561668870132921</v>
+        <v>0.08545579209214157</v>
       </c>
       <c r="C11">
-        <v>1337.515349322472</v>
+        <v>1326.898508158995</v>
       </c>
       <c r="D11">
-        <v>1382.489349322472</v>
+        <v>1387.158508158995</v>
       </c>
       <c r="E11">
-        <v>-169.226</v>
+        <v>-153.94</v>
       </c>
       <c r="F11">
-        <v>137.574</v>
+        <v>152.86</v>
       </c>
       <c r="G11">
         <v>92.59999999999999</v>
@@ -2445,28 +2445,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M11">
-        <v>7.607842199999999</v>
+        <v>8.453158</v>
       </c>
       <c r="N11">
-        <v>33.99215779999999</v>
+        <v>33.14684199999999</v>
       </c>
       <c r="O11">
-        <v>9.007921817</v>
+        <v>8.783913129999998</v>
       </c>
       <c r="P11">
-        <v>24.98423598299999</v>
+        <v>24.36292886999999</v>
       </c>
       <c r="Q11">
-        <v>104.184235983</v>
+        <v>103.56292887</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09006438868277936</v>
+        <v>0.09043471343571285</v>
       </c>
       <c r="T11">
-        <v>1.022272255953334</v>
+        <v>1.030824790663114</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.468041910753616</v>
+        <v>4.921237719678254</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08545579209214157</v>
+        <v>0.08549702048295392</v>
       </c>
       <c r="C12">
-        <v>1326.898508158995</v>
+        <v>1310.413073063093</v>
       </c>
       <c r="D12">
-        <v>1387.158508158995</v>
+        <v>1385.959073063093</v>
       </c>
       <c r="E12">
-        <v>-153.94</v>
+        <v>-138.654</v>
       </c>
       <c r="F12">
-        <v>152.86</v>
+        <v>168.146</v>
       </c>
       <c r="G12">
         <v>92.59999999999999</v>
@@ -2527,45 +2527,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M12">
-        <v>8.453158</v>
+        <v>9.7188388</v>
       </c>
       <c r="N12">
-        <v>33.14684199999999</v>
+        <v>31.88116119999999</v>
       </c>
       <c r="O12">
-        <v>8.783913129999998</v>
+        <v>8.448507717999998</v>
       </c>
       <c r="P12">
-        <v>24.36292886999999</v>
+        <v>23.432653482</v>
       </c>
       <c r="Q12">
-        <v>103.56292887</v>
+        <v>102.632653482</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09043471343571285</v>
+        <v>0.09081336009320665</v>
       </c>
       <c r="T12">
-        <v>1.030824790663114</v>
+        <v>1.039569517164126</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.265</v>
       </c>
       <c r="W12">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.921237719678254</v>
+        <v>4.280346742658185</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08549702048295392</v>
+        <v>0.08566319887376626</v>
       </c>
       <c r="C13">
-        <v>1310.413073063093</v>
+        <v>1290.313492357597</v>
       </c>
       <c r="D13">
-        <v>1385.959073063093</v>
+        <v>1381.145492357597</v>
       </c>
       <c r="E13">
-        <v>-138.654</v>
+        <v>-123.368</v>
       </c>
       <c r="F13">
-        <v>168.146</v>
+        <v>183.432</v>
       </c>
       <c r="G13">
         <v>92.59999999999999</v>
@@ -2609,45 +2609,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M13">
-        <v>9.7188388</v>
+        <v>11.2443816</v>
       </c>
       <c r="N13">
-        <v>31.88116119999999</v>
+        <v>30.3556184</v>
       </c>
       <c r="O13">
-        <v>8.448507717999998</v>
+        <v>8.044238876</v>
       </c>
       <c r="P13">
-        <v>23.432653482</v>
+        <v>22.311379524</v>
       </c>
       <c r="Q13">
-        <v>102.632653482</v>
+        <v>101.511379524</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09081336009320665</v>
+        <v>0.09120061235655258</v>
       </c>
       <c r="T13">
-        <v>1.039569517164126</v>
+        <v>1.048512987449251</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.265</v>
       </c>
       <c r="W13">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.280346742658185</v>
+        <v>3.699625420040885</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08566319887376626</v>
+        <v>0.08581394226457863</v>
       </c>
       <c r="C14">
-        <v>1290.313492357597</v>
+        <v>1270.689838301434</v>
       </c>
       <c r="D14">
-        <v>1381.145492357597</v>
+        <v>1376.807838301434</v>
       </c>
       <c r="E14">
-        <v>-123.368</v>
+        <v>-108.082</v>
       </c>
       <c r="F14">
-        <v>183.432</v>
+        <v>198.718</v>
       </c>
       <c r="G14">
         <v>92.59999999999999</v>
@@ -2691,45 +2691,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M14">
-        <v>11.2443816</v>
+        <v>12.7378238</v>
       </c>
       <c r="N14">
-        <v>30.3556184</v>
+        <v>28.86217619999999</v>
       </c>
       <c r="O14">
-        <v>8.044238876</v>
+        <v>7.648476692999998</v>
       </c>
       <c r="P14">
-        <v>22.311379524</v>
+        <v>21.21369950699999</v>
       </c>
       <c r="Q14">
-        <v>101.511379524</v>
+        <v>100.413699507</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09120061235655258</v>
+        <v>0.09159676697078004</v>
       </c>
       <c r="T14">
-        <v>1.048512987449251</v>
+        <v>1.057662054752426</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.265</v>
       </c>
       <c r="W14">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.699625420040885</v>
+        <v>3.265863985337903</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08581394226457863</v>
+        <v>0.08571772565539099</v>
       </c>
       <c r="C15">
-        <v>1270.689838301434</v>
+        <v>1258.169327961936</v>
       </c>
       <c r="D15">
-        <v>1376.807838301434</v>
+        <v>1379.573327961936</v>
       </c>
       <c r="E15">
-        <v>-108.082</v>
+        <v>-92.79599999999999</v>
       </c>
       <c r="F15">
-        <v>198.718</v>
+        <v>214.004</v>
       </c>
       <c r="G15">
         <v>92.59999999999999</v>
@@ -2773,28 +2773,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M15">
-        <v>12.7378238</v>
+        <v>13.7176564</v>
       </c>
       <c r="N15">
-        <v>28.86217619999999</v>
+        <v>27.88234359999999</v>
       </c>
       <c r="O15">
-        <v>7.648476692999998</v>
+        <v>7.388821053999998</v>
       </c>
       <c r="P15">
-        <v>21.21369950699999</v>
+        <v>20.49352254599999</v>
       </c>
       <c r="Q15">
-        <v>100.413699507</v>
+        <v>99.693522546</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09159676697078004</v>
+        <v>0.09200213448301277</v>
       </c>
       <c r="T15">
-        <v>1.057662054752426</v>
+        <v>1.067023891062651</v>
       </c>
       <c r="U15">
         <v>0.0641</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.265863985337903</v>
+        <v>3.032587986385195</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08571772565539099</v>
+        <v>0.08648145904620333</v>
       </c>
       <c r="C16">
-        <v>1258.169327961936</v>
+        <v>1221.232945777546</v>
       </c>
       <c r="D16">
-        <v>1379.573327961936</v>
+        <v>1357.922945777546</v>
       </c>
       <c r="E16">
-        <v>-92.79599999999999</v>
+        <v>-77.50999999999999</v>
       </c>
       <c r="F16">
-        <v>214.004</v>
+        <v>229.29</v>
       </c>
       <c r="G16">
         <v>92.59999999999999</v>
@@ -2855,45 +2855,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M16">
-        <v>13.7176564</v>
+        <v>16.485951</v>
       </c>
       <c r="N16">
-        <v>27.88234359999999</v>
+        <v>25.11404899999999</v>
       </c>
       <c r="O16">
-        <v>7.388821053999998</v>
+        <v>6.655222984999998</v>
       </c>
       <c r="P16">
-        <v>20.49352254599999</v>
+        <v>18.45882601499999</v>
       </c>
       <c r="Q16">
-        <v>99.693522546</v>
+        <v>97.65882601499999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09200213448301277</v>
+        <v>0.09241704005435686</v>
       </c>
       <c r="T16">
-        <v>1.067023891062651</v>
+        <v>1.076606005874292</v>
       </c>
       <c r="U16">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V16">
         <v>0.265</v>
       </c>
       <c r="W16">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.032587986385195</v>
+        <v>2.523360648105771</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08648145904620333</v>
+        <v>0.08690121243701569</v>
       </c>
       <c r="C17">
-        <v>1221.232945777546</v>
+        <v>1194.334639279649</v>
       </c>
       <c r="D17">
-        <v>1357.922945777546</v>
+        <v>1346.310639279649</v>
       </c>
       <c r="E17">
-        <v>-77.51000000000002</v>
+        <v>-62.22400000000002</v>
       </c>
       <c r="F17">
-        <v>229.29</v>
+        <v>244.576</v>
       </c>
       <c r="G17">
         <v>92.59999999999999</v>
@@ -2937,45 +2937,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M17">
-        <v>16.485951</v>
+        <v>18.5388608</v>
       </c>
       <c r="N17">
-        <v>25.11404899999999</v>
+        <v>23.06113919999999</v>
       </c>
       <c r="O17">
-        <v>6.655222984999999</v>
+        <v>6.111201887999998</v>
       </c>
       <c r="P17">
-        <v>18.458826015</v>
+        <v>16.949937312</v>
       </c>
       <c r="Q17">
-        <v>97.658826015</v>
+        <v>96.14993731199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09241704005435686</v>
+        <v>0.09284182432978058</v>
       </c>
       <c r="T17">
-        <v>1.076606005874292</v>
+        <v>1.086416266276688</v>
       </c>
       <c r="U17">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17">
         <v>0.265</v>
       </c>
       <c r="W17">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.523360648105772</v>
+        <v>2.243935075018201</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08690121243701569</v>
+        <v>0.08689099082782804</v>
       </c>
       <c r="C18">
-        <v>1194.334639279649</v>
+        <v>1179.329056156409</v>
       </c>
       <c r="D18">
-        <v>1346.310639279649</v>
+        <v>1346.591056156409</v>
       </c>
       <c r="E18">
-        <v>-62.22400000000002</v>
+        <v>-46.93799999999999</v>
       </c>
       <c r="F18">
-        <v>244.576</v>
+        <v>259.862</v>
       </c>
       <c r="G18">
         <v>92.59999999999999</v>
@@ -3019,28 +3019,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M18">
-        <v>18.5388608</v>
+        <v>19.6975396</v>
       </c>
       <c r="N18">
-        <v>23.06113919999999</v>
+        <v>21.90246039999999</v>
       </c>
       <c r="O18">
-        <v>6.111201887999998</v>
+        <v>5.804152005999998</v>
       </c>
       <c r="P18">
-        <v>16.949937312</v>
+        <v>16.09830839399999</v>
       </c>
       <c r="Q18">
-        <v>96.14993731199999</v>
+        <v>95.298308394</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09284182432978058</v>
+        <v>0.09327684437087716</v>
       </c>
       <c r="T18">
-        <v>1.086416266276688</v>
+        <v>1.096462918496008</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.243935075018201</v>
+        <v>2.111938894134778</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08689099082782804</v>
+        <v>0.08875942921864038</v>
       </c>
       <c r="C19">
-        <v>1179.329056156409</v>
+        <v>1114.654518948764</v>
       </c>
       <c r="D19">
-        <v>1346.591056156409</v>
+        <v>1297.202518948764</v>
       </c>
       <c r="E19">
-        <v>-46.93799999999999</v>
+        <v>-31.65199999999999</v>
       </c>
       <c r="F19">
-        <v>259.862</v>
+        <v>275.148</v>
       </c>
       <c r="G19">
         <v>92.59999999999999</v>
@@ -3101,45 +3101,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M19">
-        <v>19.6975396</v>
+        <v>24.76332</v>
       </c>
       <c r="N19">
-        <v>21.90246039999999</v>
+        <v>16.83667999999999</v>
       </c>
       <c r="O19">
-        <v>5.804152005999998</v>
+        <v>4.461720199999998</v>
       </c>
       <c r="P19">
-        <v>16.09830839399999</v>
+        <v>12.3749598</v>
       </c>
       <c r="Q19">
-        <v>95.298308394</v>
+        <v>91.5749598</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09327684437087716</v>
+        <v>0.09372247465687852</v>
       </c>
       <c r="T19">
-        <v>1.096462918496008</v>
+        <v>1.106754611013361</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.265</v>
       </c>
       <c r="W19">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.111938894134778</v>
+        <v>1.679903987025972</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0887594292186404</v>
+        <v>0.08885357760945274</v>
       </c>
       <c r="C20">
-        <v>1114.654518948764</v>
+        <v>1096.975586366148</v>
       </c>
       <c r="D20">
-        <v>1297.202518948764</v>
+        <v>1294.809586366148</v>
       </c>
       <c r="E20">
-        <v>-31.65200000000004</v>
+        <v>-16.36600000000004</v>
       </c>
       <c r="F20">
-        <v>275.148</v>
+        <v>290.434</v>
       </c>
       <c r="G20">
         <v>92.59999999999999</v>
@@ -3183,28 +3183,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M20">
-        <v>24.76332</v>
+        <v>26.13906</v>
       </c>
       <c r="N20">
-        <v>16.83668</v>
+        <v>15.46094</v>
       </c>
       <c r="O20">
-        <v>4.461720199999999</v>
+        <v>4.097149099999999</v>
       </c>
       <c r="P20">
-        <v>12.3749598</v>
+        <v>11.3637909</v>
       </c>
       <c r="Q20">
-        <v>91.5749598</v>
+        <v>90.5637909</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09372247465687852</v>
+        <v>0.0941791081598182</v>
       </c>
       <c r="T20">
-        <v>1.106754611013361</v>
+        <v>1.117300419395339</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.679903987025972</v>
+        <v>1.591487987708816</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08885357760945274</v>
+        <v>0.08894772600026511</v>
       </c>
       <c r="C21">
-        <v>1096.975586366148</v>
+        <v>1079.305465950945</v>
       </c>
       <c r="D21">
-        <v>1294.809586366148</v>
+        <v>1292.425465950945</v>
       </c>
       <c r="E21">
-        <v>-16.36600000000004</v>
+        <v>-1.080000000000041</v>
       </c>
       <c r="F21">
-        <v>290.434</v>
+        <v>305.72</v>
       </c>
       <c r="G21">
         <v>92.59999999999999</v>
@@ -3265,28 +3265,28 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M21">
-        <v>26.13906</v>
+        <v>27.5148</v>
       </c>
       <c r="N21">
-        <v>15.46094</v>
+        <v>14.0852</v>
       </c>
       <c r="O21">
-        <v>4.097149099999999</v>
+        <v>3.732577999999999</v>
       </c>
       <c r="P21">
-        <v>11.3637909</v>
+        <v>10.352622</v>
       </c>
       <c r="Q21">
-        <v>90.5637909</v>
+        <v>89.552622</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0941791081598182</v>
+        <v>0.09464715750033137</v>
       </c>
       <c r="T21">
-        <v>1.117300419395339</v>
+        <v>1.128109872986868</v>
       </c>
       <c r="U21">
         <v>0.09</v>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>1.591487987708816</v>
+        <v>1.511913588323375</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08894772600026511</v>
+        <v>0.09903572102912907</v>
       </c>
       <c r="C22">
-        <v>1079.305465950945</v>
+        <v>851.0492458112017</v>
       </c>
       <c r="D22">
-        <v>1292.425465950945</v>
+        <v>1079.455245811202</v>
       </c>
       <c r="E22">
-        <v>-1.080000000000041</v>
+        <v>14.20600000000002</v>
       </c>
       <c r="F22">
-        <v>305.72</v>
+        <v>321.006</v>
       </c>
       <c r="G22">
         <v>92.59999999999999</v>
@@ -3347,45 +3347,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M22">
-        <v>27.5148</v>
+        <v>47.12368080000001</v>
       </c>
       <c r="N22">
-        <v>14.0852</v>
+        <v>-5.523680800000015</v>
       </c>
       <c r="O22">
-        <v>3.732577999999999</v>
+        <v>-1.463775412000004</v>
       </c>
       <c r="P22">
-        <v>10.352622</v>
+        <v>-4.059905388000011</v>
       </c>
       <c r="Q22">
-        <v>89.552622</v>
+        <v>75.14009461199998</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09464715750033137</v>
+        <v>0.09546778334864754</v>
       </c>
       <c r="T22">
-        <v>1.128109872986868</v>
+        <v>1.147061971100405</v>
       </c>
       <c r="U22">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.265</v>
+        <v>0.2339375832458316</v>
       </c>
       <c r="W22">
-        <v>0.06615</v>
+        <v>0.1124579627795119</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.511913588323375</v>
+        <v>0.8827833330031382</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09903572102912907</v>
+        <v>0.1000457210291291</v>
       </c>
       <c r="C23">
-        <v>851.0492458112018</v>
+        <v>818.2434910411707</v>
       </c>
       <c r="D23">
-        <v>1079.455245811202</v>
+        <v>1061.935491041171</v>
       </c>
       <c r="E23">
-        <v>14.20599999999996</v>
+        <v>29.49199999999996</v>
       </c>
       <c r="F23">
-        <v>321.006</v>
+        <v>336.292</v>
       </c>
       <c r="G23">
         <v>92.59999999999999</v>
@@ -3429,37 +3429,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M23">
-        <v>47.1236808</v>
+        <v>49.3676656</v>
       </c>
       <c r="N23">
-        <v>-5.523680800000008</v>
+        <v>-7.767665600000008</v>
       </c>
       <c r="O23">
-        <v>-1.463775412000002</v>
+        <v>-2.058431384000002</v>
       </c>
       <c r="P23">
-        <v>-4.059905388000006</v>
+        <v>-5.709234216000006</v>
       </c>
       <c r="Q23">
-        <v>75.140094612</v>
+        <v>73.49076578399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09546778334864754</v>
+        <v>0.09610454980183532</v>
       </c>
       <c r="T23">
-        <v>1.147061971100405</v>
+        <v>1.16176789380682</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.2339375832458317</v>
+        <v>0.2233040567346575</v>
       </c>
       <c r="W23">
-        <v>0.1124579627795119</v>
+        <v>0.1140189644713523</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8827833330031383</v>
+        <v>0.8426568178666319</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1000457210291291</v>
+        <v>0.1010557210291291</v>
       </c>
       <c r="C24">
-        <v>818.2434910411707</v>
+        <v>785.9973512250613</v>
       </c>
       <c r="D24">
-        <v>1061.935491041171</v>
+        <v>1044.975351225061</v>
       </c>
       <c r="E24">
-        <v>29.49199999999996</v>
+        <v>44.77799999999996</v>
       </c>
       <c r="F24">
-        <v>336.292</v>
+        <v>351.578</v>
       </c>
       <c r="G24">
         <v>92.59999999999999</v>
@@ -3511,37 +3511,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M24">
-        <v>49.3676656</v>
+        <v>51.6116504</v>
       </c>
       <c r="N24">
-        <v>-7.767665600000008</v>
+        <v>-10.01165040000001</v>
       </c>
       <c r="O24">
-        <v>-2.058431384000002</v>
+        <v>-2.653087356000002</v>
       </c>
       <c r="P24">
-        <v>-5.709234216000006</v>
+        <v>-7.358563044000006</v>
       </c>
       <c r="Q24">
-        <v>73.49076578399999</v>
+        <v>71.841436956</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09610454980183532</v>
+        <v>0.0967578556434176</v>
       </c>
       <c r="T24">
-        <v>1.16176789380682</v>
+        <v>1.176855788531584</v>
       </c>
       <c r="U24">
         <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.2233040567346575</v>
+        <v>0.2135951847027159</v>
       </c>
       <c r="W24">
-        <v>0.1140189644713523</v>
+        <v>0.1154442268856413</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.8426568178666319</v>
+        <v>0.8060195649159089</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1010557210291291</v>
+        <v>0.1155708868871155</v>
       </c>
       <c r="C25">
-        <v>785.9973512250613</v>
+        <v>575.63696695896</v>
       </c>
       <c r="D25">
-        <v>1044.975351225061</v>
+        <v>849.90096695896</v>
       </c>
       <c r="E25">
-        <v>44.77799999999996</v>
+        <v>60.06400000000002</v>
       </c>
       <c r="F25">
-        <v>351.578</v>
+        <v>366.864</v>
       </c>
       <c r="G25">
         <v>92.59999999999999</v>
@@ -3593,45 +3593,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M25">
-        <v>51.6116504</v>
+        <v>73.6662912</v>
       </c>
       <c r="N25">
-        <v>-10.01165040000001</v>
+        <v>-32.06629120000001</v>
       </c>
       <c r="O25">
-        <v>-2.653087356000002</v>
+        <v>-8.497567168000003</v>
       </c>
       <c r="P25">
-        <v>-7.358563044000006</v>
+        <v>-23.56872403200001</v>
       </c>
       <c r="Q25">
-        <v>71.841436956</v>
+        <v>55.631275968</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0967578556434176</v>
+        <v>0.09814567724133942</v>
       </c>
       <c r="T25">
-        <v>1.176855788531584</v>
+        <v>1.208907095642943</v>
       </c>
       <c r="U25">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.2135951847027159</v>
+        <v>0.1496478215534217</v>
       </c>
       <c r="W25">
-        <v>0.1154442268856413</v>
+        <v>0.1707507174320729</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.8060195649159089</v>
+        <v>0.5647087605789498</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1155708868871155</v>
+        <v>0.1171208868871155</v>
       </c>
       <c r="C26">
-        <v>575.6369669589601</v>
+        <v>543.7398068901443</v>
       </c>
       <c r="D26">
-        <v>849.90096695896</v>
+        <v>833.2898068901443</v>
       </c>
       <c r="E26">
-        <v>60.06399999999996</v>
+        <v>75.34999999999997</v>
       </c>
       <c r="F26">
-        <v>366.864</v>
+        <v>382.15</v>
       </c>
       <c r="G26">
         <v>92.59999999999999</v>
@@ -3675,37 +3675,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M26">
-        <v>73.6662912</v>
+        <v>76.73572</v>
       </c>
       <c r="N26">
-        <v>-32.06629120000001</v>
+        <v>-35.13572000000001</v>
       </c>
       <c r="O26">
-        <v>-8.497567168000003</v>
+        <v>-9.310965800000002</v>
       </c>
       <c r="P26">
-        <v>-23.56872403200001</v>
+        <v>-25.8247542</v>
       </c>
       <c r="Q26">
-        <v>55.631275968</v>
+        <v>53.3752458</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09814567724133942</v>
+        <v>0.09884361960455729</v>
       </c>
       <c r="T26">
-        <v>1.208907095642943</v>
+        <v>1.225025856918182</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1496478215534217</v>
+        <v>0.1436619086912848</v>
       </c>
       <c r="W26">
-        <v>0.1707507174320729</v>
+        <v>0.17195268873479</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5647087605789498</v>
+        <v>0.5421204101557917</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1171208868871155</v>
+        <v>0.1186708868871155</v>
       </c>
       <c r="C27">
-        <v>543.7398068901443</v>
+        <v>512.4795233986436</v>
       </c>
       <c r="D27">
-        <v>833.2898068901443</v>
+        <v>817.3155233986436</v>
       </c>
       <c r="E27">
-        <v>75.34999999999997</v>
+        <v>90.63599999999997</v>
       </c>
       <c r="F27">
-        <v>382.15</v>
+        <v>397.436</v>
       </c>
       <c r="G27">
         <v>92.59999999999999</v>
@@ -3757,37 +3757,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M27">
-        <v>76.73572</v>
+        <v>79.8051488</v>
       </c>
       <c r="N27">
-        <v>-35.13572000000001</v>
+        <v>-38.2051488</v>
       </c>
       <c r="O27">
-        <v>-9.310965800000002</v>
+        <v>-10.124364432</v>
       </c>
       <c r="P27">
-        <v>-25.8247542</v>
+        <v>-28.080784368</v>
       </c>
       <c r="Q27">
-        <v>53.3752458</v>
+        <v>51.119215632</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09884361960455729</v>
+        <v>0.09956042527488915</v>
       </c>
       <c r="T27">
-        <v>1.225025856918182</v>
+        <v>1.241580260390049</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1436619086912848</v>
+        <v>0.138136450664697</v>
       </c>
       <c r="W27">
-        <v>0.17195268873479</v>
+        <v>0.1730622007065289</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5421204101557917</v>
+        <v>0.5212696251497998</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1186708868871155</v>
+        <v>0.1202208868871155</v>
       </c>
       <c r="C28">
-        <v>512.4795233986436</v>
+        <v>481.8201783807153</v>
       </c>
       <c r="D28">
-        <v>817.3155233986436</v>
+        <v>801.9421783807153</v>
       </c>
       <c r="E28">
-        <v>90.63599999999997</v>
+        <v>105.922</v>
       </c>
       <c r="F28">
-        <v>397.436</v>
+        <v>412.722</v>
       </c>
       <c r="G28">
         <v>92.59999999999999</v>
@@ -3839,37 +3839,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M28">
-        <v>79.8051488</v>
+        <v>82.87457759999999</v>
       </c>
       <c r="N28">
-        <v>-38.2051488</v>
+        <v>-41.2745776</v>
       </c>
       <c r="O28">
-        <v>-10.124364432</v>
+        <v>-10.937763064</v>
       </c>
       <c r="P28">
-        <v>-28.080784368</v>
+        <v>-30.336814536</v>
       </c>
       <c r="Q28">
-        <v>51.119215632</v>
+        <v>48.863185464</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09956042527488915</v>
+        <v>0.1002968694567369</v>
       </c>
       <c r="T28">
-        <v>1.241580260390049</v>
+        <v>1.258588209162516</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.138136450664697</v>
+        <v>0.1330202858252637</v>
       </c>
       <c r="W28">
-        <v>0.1730622007065289</v>
+        <v>0.174089526606287</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.5212696251497998</v>
+        <v>0.5019633427368443</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1202208868871155</v>
+        <v>0.1317908678956863</v>
       </c>
       <c r="C29">
-        <v>481.8201783807153</v>
+        <v>367.8008252058434</v>
       </c>
       <c r="D29">
-        <v>801.9421783807153</v>
+        <v>703.2088252058434</v>
       </c>
       <c r="E29">
-        <v>105.922</v>
+        <v>121.208</v>
       </c>
       <c r="F29">
-        <v>412.722</v>
+        <v>428.008</v>
       </c>
       <c r="G29">
         <v>92.59999999999999</v>
@@ -3921,45 +3921,45 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M29">
-        <v>82.87457759999999</v>
+        <v>100.9242864</v>
       </c>
       <c r="N29">
-        <v>-41.2745776</v>
+        <v>-59.32428640000002</v>
       </c>
       <c r="O29">
-        <v>-10.937763064</v>
+        <v>-15.72093589600001</v>
       </c>
       <c r="P29">
-        <v>-30.336814536</v>
+        <v>-43.60335050400001</v>
       </c>
       <c r="Q29">
-        <v>48.863185464</v>
+        <v>35.59664949599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1002968694567369</v>
+        <v>0.1013592995999844</v>
       </c>
       <c r="T29">
-        <v>1.258588209162516</v>
+        <v>1.283124702078163</v>
       </c>
       <c r="U29">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1330202858252637</v>
+        <v>0.1092303982839952</v>
       </c>
       <c r="W29">
-        <v>0.174089526606287</v>
+        <v>0.2100434720846339</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.5019633427368443</v>
+        <v>0.4121901822037554</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1317908678956863</v>
+        <v>0.1336908678956863</v>
       </c>
       <c r="C30">
-        <v>367.8008252058434</v>
+        <v>338.5789886132879</v>
       </c>
       <c r="D30">
-        <v>703.2088252058434</v>
+        <v>689.2729886132879</v>
       </c>
       <c r="E30">
-        <v>121.208</v>
+        <v>136.494</v>
       </c>
       <c r="F30">
-        <v>428.008</v>
+        <v>443.294</v>
       </c>
       <c r="G30">
         <v>92.59999999999999</v>
@@ -4003,37 +4003,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M30">
-        <v>100.9242864</v>
+        <v>104.5287252</v>
       </c>
       <c r="N30">
-        <v>-59.32428640000002</v>
+        <v>-62.92872520000002</v>
       </c>
       <c r="O30">
-        <v>-15.72093589600001</v>
+        <v>-16.676112178</v>
       </c>
       <c r="P30">
-        <v>-43.60335050400001</v>
+        <v>-46.25261302200001</v>
       </c>
       <c r="Q30">
-        <v>35.59664949599999</v>
+        <v>32.94738697799999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1013592995999844</v>
+        <v>0.1021418249464631</v>
       </c>
       <c r="T30">
-        <v>1.283124702078163</v>
+        <v>1.301196880980672</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.1092303982839952</v>
+        <v>0.1054638328259264</v>
       </c>
       <c r="W30">
-        <v>0.2100434720846339</v>
+        <v>0.2109316282196466</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4121901822037554</v>
+        <v>0.3979767276450051</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1336908678956863</v>
+        <v>0.1355908678956863</v>
       </c>
       <c r="C31">
-        <v>338.578988613288</v>
+        <v>309.898765315454</v>
       </c>
       <c r="D31">
-        <v>689.2729886132879</v>
+        <v>675.878765315454</v>
       </c>
       <c r="E31">
-        <v>136.4939999999999</v>
+        <v>151.78</v>
       </c>
       <c r="F31">
-        <v>443.2939999999999</v>
+        <v>458.58</v>
       </c>
       <c r="G31">
         <v>92.59999999999999</v>
@@ -4085,37 +4085,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M31">
-        <v>104.5287252</v>
+        <v>108.133164</v>
       </c>
       <c r="N31">
-        <v>-62.92872519999999</v>
+        <v>-66.533164</v>
       </c>
       <c r="O31">
-        <v>-16.676112178</v>
+        <v>-17.63128846</v>
       </c>
       <c r="P31">
-        <v>-46.25261302199999</v>
+        <v>-48.90187554</v>
       </c>
       <c r="Q31">
-        <v>32.94738697800001</v>
+        <v>30.29812446</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1021418249464631</v>
+        <v>0.102946708159984</v>
       </c>
       <c r="T31">
-        <v>1.301196880980672</v>
+        <v>1.319785407851824</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.1054638328259264</v>
+        <v>0.1019483717317289</v>
       </c>
       <c r="W31">
-        <v>0.2109316282196466</v>
+        <v>0.2117605739456583</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3979767276450052</v>
+        <v>0.384710836723505</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1355908678956863</v>
+        <v>0.1374908678956863</v>
       </c>
       <c r="C32">
-        <v>309.898765315454</v>
+        <v>281.7291826586265</v>
       </c>
       <c r="D32">
-        <v>675.878765315454</v>
+        <v>662.9951826586265</v>
       </c>
       <c r="E32">
-        <v>151.78</v>
+        <v>167.066</v>
       </c>
       <c r="F32">
-        <v>458.58</v>
+        <v>473.866</v>
       </c>
       <c r="G32">
         <v>92.59999999999999</v>
@@ -4167,37 +4167,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M32">
-        <v>108.133164</v>
+        <v>111.7376028</v>
       </c>
       <c r="N32">
-        <v>-66.533164</v>
+        <v>-70.13760280000001</v>
       </c>
       <c r="O32">
-        <v>-17.63128846</v>
+        <v>-18.586464742</v>
       </c>
       <c r="P32">
-        <v>-48.90187554</v>
+        <v>-51.55113805800001</v>
       </c>
       <c r="Q32">
-        <v>30.29812446</v>
+        <v>27.648861942</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.102946708159984</v>
+        <v>0.1037749213217229</v>
       </c>
       <c r="T32">
-        <v>1.319785407851824</v>
+        <v>1.3389127326033</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1019483717317289</v>
+        <v>0.09865971457909242</v>
       </c>
       <c r="W32">
-        <v>0.2117605739456583</v>
+        <v>0.21253603930225</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.384710836723505</v>
+        <v>0.3723008097324242</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1374908678956863</v>
+        <v>0.1393908678956863</v>
       </c>
       <c r="C33">
-        <v>281.7291826586265</v>
+        <v>254.0415854139343</v>
       </c>
       <c r="D33">
-        <v>662.9951826586265</v>
+        <v>650.5935854139343</v>
       </c>
       <c r="E33">
-        <v>167.066</v>
+        <v>182.352</v>
       </c>
       <c r="F33">
-        <v>473.866</v>
+        <v>489.152</v>
       </c>
       <c r="G33">
         <v>92.59999999999999</v>
@@ -4249,37 +4249,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M33">
-        <v>111.7376028</v>
+        <v>115.3420416</v>
       </c>
       <c r="N33">
-        <v>-70.13760280000001</v>
+        <v>-73.74204160000001</v>
       </c>
       <c r="O33">
-        <v>-18.586464742</v>
+        <v>-19.541641024</v>
       </c>
       <c r="P33">
-        <v>-51.55113805800001</v>
+        <v>-54.20040057600001</v>
       </c>
       <c r="Q33">
-        <v>27.648861942</v>
+        <v>24.999599424</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1037749213217229</v>
+        <v>0.1046274936941012</v>
       </c>
       <c r="T33">
-        <v>1.3389127326033</v>
+        <v>1.358602625729819</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.09865971457909242</v>
+        <v>0.09557659849849579</v>
       </c>
       <c r="W33">
-        <v>0.21253603930225</v>
+        <v>0.2132630380740547</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3723008097324242</v>
+        <v>0.360666409428286</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1393908678956863</v>
+        <v>0.1412908678956863</v>
       </c>
       <c r="C34">
-        <v>254.0415854139343</v>
+        <v>226.8094230152346</v>
       </c>
       <c r="D34">
-        <v>650.5935854139343</v>
+        <v>638.6474230152346</v>
       </c>
       <c r="E34">
-        <v>182.352</v>
+        <v>197.638</v>
       </c>
       <c r="F34">
-        <v>489.152</v>
+        <v>504.438</v>
       </c>
       <c r="G34">
         <v>92.59999999999999</v>
@@ -4331,37 +4331,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M34">
-        <v>115.3420416</v>
+        <v>118.9464804</v>
       </c>
       <c r="N34">
-        <v>-73.74204160000001</v>
+        <v>-77.3464804</v>
       </c>
       <c r="O34">
-        <v>-19.541641024</v>
+        <v>-20.496817306</v>
       </c>
       <c r="P34">
-        <v>-54.20040057600001</v>
+        <v>-56.84966309400001</v>
       </c>
       <c r="Q34">
-        <v>24.999599424</v>
+        <v>22.350336906</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1046274936941012</v>
+        <v>0.105505515988043</v>
       </c>
       <c r="T34">
-        <v>1.358602625729819</v>
+        <v>1.378880276860115</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.09557659849849579</v>
+        <v>0.0926803379379353</v>
       </c>
       <c r="W34">
-        <v>0.2132630380740547</v>
+        <v>0.2139459763142349</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.360666409428286</v>
+        <v>0.3497371242940955</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1412908678956863</v>
+        <v>0.1431908678956863</v>
       </c>
       <c r="C35">
-        <v>226.8094230152346</v>
+        <v>200.0080598147028</v>
       </c>
       <c r="D35">
-        <v>638.6474230152346</v>
+        <v>627.1320598147029</v>
       </c>
       <c r="E35">
-        <v>197.638</v>
+        <v>212.924</v>
       </c>
       <c r="F35">
-        <v>504.438</v>
+        <v>519.724</v>
       </c>
       <c r="G35">
         <v>92.59999999999999</v>
@@ -4413,37 +4413,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M35">
-        <v>118.9464804</v>
+        <v>122.5509192</v>
       </c>
       <c r="N35">
-        <v>-77.3464804</v>
+        <v>-80.95091920000002</v>
       </c>
       <c r="O35">
-        <v>-20.496817306</v>
+        <v>-21.451993588</v>
       </c>
       <c r="P35">
-        <v>-56.84966309400001</v>
+        <v>-59.49892561200001</v>
       </c>
       <c r="Q35">
-        <v>22.350336906</v>
+        <v>19.70107438799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.105505515988043</v>
+        <v>0.1064101450181648</v>
       </c>
       <c r="T35">
-        <v>1.378880276860115</v>
+        <v>1.399772402267087</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.0926803379379353</v>
+        <v>0.08995444564564309</v>
       </c>
       <c r="W35">
-        <v>0.2139459763142349</v>
+        <v>0.2145887417167573</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3497371242940955</v>
+        <v>0.3394507382854456</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1431908678956863</v>
+        <v>0.1450908678956863</v>
       </c>
       <c r="C36">
-        <v>200.0080598147028</v>
+        <v>173.6146055023806</v>
       </c>
       <c r="D36">
-        <v>627.1320598147029</v>
+        <v>616.0246055023806</v>
       </c>
       <c r="E36">
-        <v>212.924</v>
+        <v>228.21</v>
       </c>
       <c r="F36">
-        <v>519.724</v>
+        <v>535.01</v>
       </c>
       <c r="G36">
         <v>92.59999999999999</v>
@@ -4495,37 +4495,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M36">
-        <v>122.5509192</v>
+        <v>126.155358</v>
       </c>
       <c r="N36">
-        <v>-80.95091920000002</v>
+        <v>-84.55535800000001</v>
       </c>
       <c r="O36">
-        <v>-21.451993588</v>
+        <v>-22.40716987</v>
       </c>
       <c r="P36">
-        <v>-59.49892561200001</v>
+        <v>-62.14818813000001</v>
       </c>
       <c r="Q36">
-        <v>19.70107438799999</v>
+        <v>17.05181186999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1064101450181648</v>
+        <v>0.1073426087876751</v>
       </c>
       <c r="T36">
-        <v>1.399772402267087</v>
+        <v>1.421307362301965</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.08995444564564309</v>
+        <v>0.08738431862719614</v>
       </c>
       <c r="W36">
-        <v>0.2145887417167573</v>
+        <v>0.2151947776677072</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3394507382854456</v>
+        <v>0.3297521457630043</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1450908678956863</v>
+        <v>0.1469908678956863</v>
       </c>
       <c r="C37">
-        <v>173.6146055023806</v>
+        <v>147.6077632332473</v>
       </c>
       <c r="D37">
-        <v>616.0246055023806</v>
+        <v>605.3037632332473</v>
       </c>
       <c r="E37">
-        <v>228.21</v>
+        <v>243.496</v>
       </c>
       <c r="F37">
-        <v>535.01</v>
+        <v>550.296</v>
       </c>
       <c r="G37">
         <v>92.59999999999999</v>
@@ -4577,37 +4577,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M37">
-        <v>126.155358</v>
+        <v>129.7597968</v>
       </c>
       <c r="N37">
-        <v>-84.55535800000001</v>
+        <v>-88.15979680000001</v>
       </c>
       <c r="O37">
-        <v>-22.40716987</v>
+        <v>-23.362346152</v>
       </c>
       <c r="P37">
-        <v>-62.14818813000001</v>
+        <v>-64.79745064800001</v>
       </c>
       <c r="Q37">
-        <v>17.05181186999999</v>
+        <v>14.40254935199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1073426087876751</v>
+        <v>0.1083042120499825</v>
       </c>
       <c r="T37">
-        <v>1.421307362301965</v>
+        <v>1.443515289837933</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.08738431862719614</v>
+        <v>0.08495697644310736</v>
       </c>
       <c r="W37">
-        <v>0.2151947776677072</v>
+        <v>0.2157671449547153</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3297521457630043</v>
+        <v>0.3205923639362542</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1469908678956863</v>
+        <v>0.1488908678956863</v>
       </c>
       <c r="C38">
-        <v>147.6077632332476</v>
+        <v>121.967693341539</v>
       </c>
       <c r="D38">
-        <v>605.3037632332475</v>
+        <v>594.9496933415389</v>
       </c>
       <c r="E38">
-        <v>243.4959999999999</v>
+        <v>258.782</v>
       </c>
       <c r="F38">
-        <v>550.2959999999999</v>
+        <v>565.582</v>
       </c>
       <c r="G38">
         <v>92.59999999999999</v>
@@ -4659,37 +4659,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M38">
-        <v>129.7597968</v>
+        <v>133.3642356</v>
       </c>
       <c r="N38">
-        <v>-88.15979680000001</v>
+        <v>-91.76423560000001</v>
       </c>
       <c r="O38">
-        <v>-23.362346152</v>
+        <v>-24.317522434</v>
       </c>
       <c r="P38">
-        <v>-64.79745064800001</v>
+        <v>-67.44671316599999</v>
       </c>
       <c r="Q38">
-        <v>14.40254935199999</v>
+        <v>11.75328683400001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1083042120499825</v>
+        <v>0.1092963423999822</v>
       </c>
       <c r="T38">
-        <v>1.443515289837933</v>
+        <v>1.466428230946472</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.08495697644310736</v>
+        <v>0.082660841944645</v>
       </c>
       <c r="W38">
-        <v>0.2157671449547153</v>
+        <v>0.2163085734694527</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3205923639362542</v>
+        <v>0.3119277054514906</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1488908678956863</v>
+        <v>0.1507908678956863</v>
       </c>
       <c r="C39">
-        <v>121.967693341539</v>
+        <v>96.67589080729499</v>
       </c>
       <c r="D39">
-        <v>594.9496933415389</v>
+        <v>584.9438908072949</v>
       </c>
       <c r="E39">
-        <v>258.782</v>
+        <v>274.0679999999999</v>
       </c>
       <c r="F39">
-        <v>565.582</v>
+        <v>580.8679999999999</v>
       </c>
       <c r="G39">
         <v>92.59999999999999</v>
@@ -4741,37 +4741,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M39">
-        <v>133.3642356</v>
+        <v>136.9686744</v>
       </c>
       <c r="N39">
-        <v>-91.76423560000001</v>
+        <v>-95.3686744</v>
       </c>
       <c r="O39">
-        <v>-24.317522434</v>
+        <v>-25.272698716</v>
       </c>
       <c r="P39">
-        <v>-67.44671316599999</v>
+        <v>-70.095975684</v>
       </c>
       <c r="Q39">
-        <v>11.75328683400001</v>
+        <v>9.104024316000007</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1092963423999822</v>
+        <v>0.1103204769548206</v>
       </c>
       <c r="T39">
-        <v>1.466428230946472</v>
+        <v>1.490080299187544</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.082660841944645</v>
+        <v>0.08048555663031225</v>
       </c>
       <c r="W39">
-        <v>0.2163085734694527</v>
+        <v>0.2168215057465724</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3119277054514906</v>
+        <v>0.3037190816238198</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1507908678956863</v>
+        <v>0.1526908678956863</v>
       </c>
       <c r="C40">
-        <v>96.67589080729499</v>
+        <v>71.71507488293162</v>
       </c>
       <c r="D40">
-        <v>584.9438908072949</v>
+        <v>575.2690748829316</v>
       </c>
       <c r="E40">
-        <v>274.0679999999999</v>
+        <v>289.354</v>
       </c>
       <c r="F40">
-        <v>580.8679999999999</v>
+        <v>596.154</v>
       </c>
       <c r="G40">
         <v>92.59999999999999</v>
@@ -4823,37 +4823,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M40">
-        <v>136.9686744</v>
+        <v>140.5731132</v>
       </c>
       <c r="N40">
-        <v>-95.3686744</v>
+        <v>-98.9731132</v>
       </c>
       <c r="O40">
-        <v>-25.272698716</v>
+        <v>-26.227874998</v>
       </c>
       <c r="P40">
-        <v>-70.095975684</v>
+        <v>-72.745238202</v>
       </c>
       <c r="Q40">
-        <v>9.104024316000007</v>
+        <v>6.454761798000007</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1103204769548206</v>
+        <v>0.1113781896917849</v>
       </c>
       <c r="T40">
-        <v>1.490080299187544</v>
+        <v>1.514507845075864</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08048555663031225</v>
+        <v>0.07842182440902219</v>
       </c>
       <c r="W40">
-        <v>0.2168215057465724</v>
+        <v>0.2173081338043526</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3037190816238198</v>
+        <v>0.2959314128642346</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1526908678956863</v>
+        <v>0.1545908678956863</v>
       </c>
       <c r="C41">
-        <v>71.71507488293162</v>
+        <v>47.06908949487865</v>
       </c>
       <c r="D41">
-        <v>575.2690748829316</v>
+        <v>565.9090894948786</v>
       </c>
       <c r="E41">
-        <v>289.354</v>
+        <v>304.6399999999999</v>
       </c>
       <c r="F41">
-        <v>596.154</v>
+        <v>611.4399999999999</v>
       </c>
       <c r="G41">
         <v>92.59999999999999</v>
@@ -4905,37 +4905,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M41">
-        <v>140.5731132</v>
+        <v>144.177552</v>
       </c>
       <c r="N41">
-        <v>-98.9731132</v>
+        <v>-102.577552</v>
       </c>
       <c r="O41">
-        <v>-26.227874998</v>
+        <v>-27.18305128</v>
       </c>
       <c r="P41">
-        <v>-72.745238202</v>
+        <v>-75.39450072</v>
       </c>
       <c r="Q41">
-        <v>6.454761798000007</v>
+        <v>3.805499280000006</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1113781896917849</v>
+        <v>0.1124711595199813</v>
       </c>
       <c r="T41">
-        <v>1.514507845075864</v>
+        <v>1.539749642493795</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07842182440902219</v>
+        <v>0.07646127879879665</v>
       </c>
       <c r="W41">
-        <v>0.2173081338043526</v>
+        <v>0.2177704304592438</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2959314128642346</v>
+        <v>0.2885331275426288</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1545908678956863</v>
+        <v>0.1564908678956863</v>
       </c>
       <c r="C42">
-        <v>47.06908949487865</v>
+        <v>22.72281321271225</v>
       </c>
       <c r="D42">
-        <v>565.9090894948786</v>
+        <v>556.8488132127122</v>
       </c>
       <c r="E42">
-        <v>304.6399999999999</v>
+        <v>319.926</v>
       </c>
       <c r="F42">
-        <v>611.4399999999999</v>
+        <v>626.726</v>
       </c>
       <c r="G42">
         <v>92.59999999999999</v>
@@ -4987,37 +4987,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M42">
-        <v>144.177552</v>
+        <v>147.7819908</v>
       </c>
       <c r="N42">
-        <v>-102.577552</v>
+        <v>-106.1819908</v>
       </c>
       <c r="O42">
-        <v>-27.18305128</v>
+        <v>-28.13822756200001</v>
       </c>
       <c r="P42">
-        <v>-75.39450072</v>
+        <v>-78.04376323800001</v>
       </c>
       <c r="Q42">
-        <v>3.805499280000006</v>
+        <v>1.156236761999992</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1124711595199813</v>
+        <v>0.1136011791728624</v>
       </c>
       <c r="T42">
-        <v>1.539749642493795</v>
+        <v>1.565847094061487</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.07646127879879665</v>
+        <v>0.07459636955980159</v>
       </c>
       <c r="W42">
-        <v>0.2177704304592438</v>
+        <v>0.2182101760577988</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2885331275426288</v>
+        <v>0.2814957341879305</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1564908678956863</v>
+        <v>0.1583908678956863</v>
       </c>
       <c r="C43">
-        <v>22.72281321271225</v>
+        <v>-1.337922269560181</v>
       </c>
       <c r="D43">
-        <v>556.8488132127122</v>
+        <v>548.0740777304399</v>
       </c>
       <c r="E43">
-        <v>319.926</v>
+        <v>335.212</v>
       </c>
       <c r="F43">
-        <v>626.726</v>
+        <v>642.0120000000001</v>
       </c>
       <c r="G43">
         <v>92.59999999999999</v>
@@ -5069,37 +5069,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M43">
-        <v>147.7819908</v>
+        <v>151.3864296</v>
       </c>
       <c r="N43">
-        <v>-106.1819908</v>
+        <v>-109.7864296</v>
       </c>
       <c r="O43">
-        <v>-28.13822756200001</v>
+        <v>-29.09340384400001</v>
       </c>
       <c r="P43">
-        <v>-78.04376323800001</v>
+        <v>-80.69302575600001</v>
       </c>
       <c r="Q43">
-        <v>1.156236761999992</v>
+        <v>-1.493025756000009</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1136011791728624</v>
+        <v>0.1147701650206703</v>
       </c>
       <c r="T43">
-        <v>1.565847094061487</v>
+        <v>1.592844457752202</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07459636955980159</v>
+        <v>0.07282026552266345</v>
       </c>
       <c r="W43">
-        <v>0.2182101760577988</v>
+        <v>0.218628981389756</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2814957341879305</v>
+        <v>0.2747934548025036</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1583908678956863</v>
+        <v>0.1602908678956863</v>
       </c>
       <c r="C44">
-        <v>-1.337922269560067</v>
+        <v>-25.12640606442847</v>
       </c>
       <c r="D44">
-        <v>548.0740777304399</v>
+        <v>539.5715939355715</v>
       </c>
       <c r="E44">
-        <v>335.2119999999999</v>
+        <v>350.498</v>
       </c>
       <c r="F44">
-        <v>642.0119999999999</v>
+        <v>657.298</v>
       </c>
       <c r="G44">
         <v>92.59999999999999</v>
@@ -5151,37 +5151,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M44">
-        <v>151.3864296</v>
+        <v>154.9908684</v>
       </c>
       <c r="N44">
-        <v>-109.7864296</v>
+        <v>-113.3908684</v>
       </c>
       <c r="O44">
-        <v>-29.093403844</v>
+        <v>-30.048580126</v>
       </c>
       <c r="P44">
-        <v>-80.693025756</v>
+        <v>-83.34228827400001</v>
       </c>
       <c r="Q44">
-        <v>-1.493025755999994</v>
+        <v>-4.142288274000009</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1147701650206703</v>
+        <v>0.1159801679157698</v>
       </c>
       <c r="T44">
-        <v>1.592844457752202</v>
+        <v>1.62078909736189</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07282026552266346</v>
+        <v>0.07112677097562477</v>
       </c>
       <c r="W44">
-        <v>0.2186289813897559</v>
+        <v>0.2190283074039477</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2747934548025036</v>
+        <v>0.2684029093419803</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1602908678956863</v>
+        <v>0.1621908678956863</v>
       </c>
       <c r="C45">
-        <v>-25.12640606442847</v>
+        <v>-48.65511524541853</v>
       </c>
       <c r="D45">
-        <v>539.5715939355715</v>
+        <v>531.3288847545814</v>
       </c>
       <c r="E45">
-        <v>350.498</v>
+        <v>365.7839999999999</v>
       </c>
       <c r="F45">
-        <v>657.298</v>
+        <v>672.5839999999999</v>
       </c>
       <c r="G45">
         <v>92.59999999999999</v>
@@ -5233,37 +5233,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M45">
-        <v>154.9908684</v>
+        <v>158.5953072</v>
       </c>
       <c r="N45">
-        <v>-113.3908684</v>
+        <v>-116.9953072</v>
       </c>
       <c r="O45">
-        <v>-30.048580126</v>
+        <v>-31.003756408</v>
       </c>
       <c r="P45">
-        <v>-83.34228827400001</v>
+        <v>-85.99155079200001</v>
       </c>
       <c r="Q45">
-        <v>-4.142288274000009</v>
+        <v>-6.79155079200001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1159801679157698</v>
+        <v>0.11723338519998</v>
       </c>
       <c r="T45">
-        <v>1.62078909736189</v>
+        <v>1.64973175981478</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07112677097562477</v>
+        <v>0.06951025345345148</v>
       </c>
       <c r="W45">
-        <v>0.2190283074039477</v>
+        <v>0.2194094822356761</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2684029093419803</v>
+        <v>0.2623028432205716</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1621908678956863</v>
+        <v>0.1640908678956863</v>
       </c>
       <c r="C46">
-        <v>-48.65511524541853</v>
+        <v>-71.93577593897101</v>
       </c>
       <c r="D46">
-        <v>531.3288847545814</v>
+        <v>523.334224061029</v>
       </c>
       <c r="E46">
-        <v>365.7839999999999</v>
+        <v>381.07</v>
       </c>
       <c r="F46">
-        <v>672.5839999999999</v>
+        <v>687.87</v>
       </c>
       <c r="G46">
         <v>92.59999999999999</v>
@@ -5315,37 +5315,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M46">
-        <v>158.5953072</v>
+        <v>162.199746</v>
       </c>
       <c r="N46">
-        <v>-116.9953072</v>
+        <v>-120.599746</v>
       </c>
       <c r="O46">
-        <v>-31.003756408</v>
+        <v>-31.95893269</v>
       </c>
       <c r="P46">
-        <v>-85.99155079200001</v>
+        <v>-88.64081331</v>
       </c>
       <c r="Q46">
-        <v>-6.79155079200001</v>
+        <v>-9.440813309999996</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.11723338519998</v>
+        <v>0.1185321740217978</v>
       </c>
       <c r="T46">
-        <v>1.64973175981478</v>
+        <v>1.679726882720504</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06951025345345148</v>
+        <v>0.06796558115448589</v>
       </c>
       <c r="W46">
-        <v>0.2194094822356761</v>
+        <v>0.2197737159637722</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2623028432205716</v>
+        <v>0.2564738911490033</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1640908678956863</v>
+        <v>0.1659908678956863</v>
       </c>
       <c r="C47">
-        <v>-71.93577593897101</v>
+        <v>-94.97941898274883</v>
       </c>
       <c r="D47">
-        <v>523.334224061029</v>
+        <v>515.5765810172511</v>
       </c>
       <c r="E47">
-        <v>381.07</v>
+        <v>396.3559999999999</v>
       </c>
       <c r="F47">
-        <v>687.87</v>
+        <v>703.1559999999999</v>
       </c>
       <c r="G47">
         <v>92.59999999999999</v>
@@ -5397,37 +5397,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M47">
-        <v>162.199746</v>
+        <v>165.8041848</v>
       </c>
       <c r="N47">
-        <v>-120.599746</v>
+        <v>-124.2041848</v>
       </c>
       <c r="O47">
-        <v>-31.95893269</v>
+        <v>-32.914108972</v>
       </c>
       <c r="P47">
-        <v>-88.64081331</v>
+        <v>-91.290075828</v>
       </c>
       <c r="Q47">
-        <v>-9.440813309999996</v>
+        <v>-12.090075828</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1185321740217978</v>
+        <v>0.1198790661333126</v>
       </c>
       <c r="T47">
-        <v>1.679726882720504</v>
+        <v>1.710832936104217</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06796558115448589</v>
+        <v>0.06648806852069272</v>
       </c>
       <c r="W47">
-        <v>0.2197737159637722</v>
+        <v>0.2201221134428206</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2564738911490033</v>
+        <v>0.2508983717761989</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1659908678956863</v>
+        <v>0.1678908678956863</v>
       </c>
       <c r="C48">
-        <v>-94.97941898274883</v>
+        <v>-117.7964307059507</v>
       </c>
       <c r="D48">
-        <v>515.5765810172511</v>
+        <v>508.0455692940494</v>
       </c>
       <c r="E48">
-        <v>396.3559999999999</v>
+        <v>411.642</v>
       </c>
       <c r="F48">
-        <v>703.1559999999999</v>
+        <v>718.442</v>
       </c>
       <c r="G48">
         <v>92.59999999999999</v>
@@ -5479,37 +5479,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M48">
-        <v>165.8041848</v>
+        <v>169.4086236</v>
       </c>
       <c r="N48">
-        <v>-124.2041848</v>
+        <v>-127.8086236</v>
       </c>
       <c r="O48">
-        <v>-32.914108972</v>
+        <v>-33.869285254</v>
       </c>
       <c r="P48">
-        <v>-91.290075828</v>
+        <v>-93.939338346</v>
       </c>
       <c r="Q48">
-        <v>-12.090075828</v>
+        <v>-14.739338346</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1198790661333126</v>
+        <v>0.121276784362243</v>
       </c>
       <c r="T48">
-        <v>1.710832936104217</v>
+        <v>1.743112802823164</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06648806852069272</v>
+        <v>0.0650734287649333</v>
       </c>
       <c r="W48">
-        <v>0.2201221134428206</v>
+        <v>0.2204556854972287</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2508983717761989</v>
+        <v>0.2455601085469181</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1678908678956863</v>
+        <v>0.1697908678956863</v>
       </c>
       <c r="C49">
-        <v>-117.7964307059507</v>
+        <v>-140.3965993232138</v>
       </c>
       <c r="D49">
-        <v>508.0455692940494</v>
+        <v>500.7314006767863</v>
       </c>
       <c r="E49">
-        <v>411.642</v>
+        <v>426.9280000000001</v>
       </c>
       <c r="F49">
-        <v>718.442</v>
+        <v>733.7280000000001</v>
       </c>
       <c r="G49">
         <v>92.59999999999999</v>
@@ -5561,37 +5561,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M49">
-        <v>169.4086236</v>
+        <v>173.0130624</v>
       </c>
       <c r="N49">
-        <v>-127.8086236</v>
+        <v>-131.4130624</v>
       </c>
       <c r="O49">
-        <v>-33.869285254</v>
+        <v>-34.82446153600001</v>
       </c>
       <c r="P49">
-        <v>-93.939338346</v>
+        <v>-96.58860086400003</v>
       </c>
       <c r="Q49">
-        <v>-14.739338346</v>
+        <v>-17.38860086400003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.121276784362243</v>
+        <v>0.1227282609845938</v>
       </c>
       <c r="T49">
-        <v>1.743112802823164</v>
+        <v>1.776634202877456</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0650734287649333</v>
+        <v>0.06371773233233052</v>
       </c>
       <c r="W49">
-        <v>0.2204556854972287</v>
+        <v>0.2207753587160365</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2455601085469181</v>
+        <v>0.2404442729521906</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1697908678956863</v>
+        <v>0.1716908678956863</v>
       </c>
       <c r="C50">
-        <v>-140.3965993232135</v>
+        <v>-162.7891573778874</v>
       </c>
       <c r="D50">
-        <v>500.7314006767864</v>
+        <v>493.6248426221126</v>
       </c>
       <c r="E50">
-        <v>426.9279999999999</v>
+        <v>442.2139999999999</v>
       </c>
       <c r="F50">
-        <v>733.728</v>
+        <v>749.0139999999999</v>
       </c>
       <c r="G50">
         <v>92.59999999999999</v>
@@ -5643,37 +5643,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M50">
-        <v>173.0130624</v>
+        <v>176.6175012</v>
       </c>
       <c r="N50">
-        <v>-131.4130624</v>
+        <v>-135.0175012</v>
       </c>
       <c r="O50">
-        <v>-34.824461536</v>
+        <v>-35.779637818</v>
       </c>
       <c r="P50">
-        <v>-96.588600864</v>
+        <v>-99.237863382</v>
       </c>
       <c r="Q50">
-        <v>-17.388600864</v>
+        <v>-20.037863382</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1227282609845938</v>
+        <v>0.1242366582588016</v>
       </c>
       <c r="T50">
-        <v>1.776634202877456</v>
+        <v>1.811470167639759</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06371773233233054</v>
+        <v>0.06241737044799726</v>
       </c>
       <c r="W50">
-        <v>0.2207753587160365</v>
+        <v>0.2210819840483623</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2404442729521906</v>
+        <v>0.2355372469735745</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1716908678956863</v>
+        <v>0.1735908678956863</v>
       </c>
       <c r="C51">
-        <v>-162.7891573778874</v>
+        <v>-184.982820621663</v>
       </c>
       <c r="D51">
-        <v>493.6248426221126</v>
+        <v>486.7171793783369</v>
       </c>
       <c r="E51">
-        <v>442.2139999999999</v>
+        <v>457.4999999999999</v>
       </c>
       <c r="F51">
-        <v>749.0139999999999</v>
+        <v>764.3</v>
       </c>
       <c r="G51">
         <v>92.59999999999999</v>
@@ -5725,37 +5725,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M51">
-        <v>176.6175012</v>
+        <v>180.22194</v>
       </c>
       <c r="N51">
-        <v>-135.0175012</v>
+        <v>-138.62194</v>
       </c>
       <c r="O51">
-        <v>-35.779637818</v>
+        <v>-36.7348141</v>
       </c>
       <c r="P51">
-        <v>-99.237863382</v>
+        <v>-101.8871259</v>
       </c>
       <c r="Q51">
-        <v>-20.037863382</v>
+        <v>-22.6871259</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1242366582588016</v>
+        <v>0.1258053914239776</v>
       </c>
       <c r="T51">
-        <v>1.811470167639759</v>
+        <v>1.847699570992554</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06241737044799726</v>
+        <v>0.06116902303903731</v>
       </c>
       <c r="W51">
-        <v>0.2210819840483623</v>
+        <v>0.221376344367395</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2355372469735745</v>
+        <v>0.230826502034103</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1735908678956863</v>
+        <v>0.1754908678956863</v>
       </c>
       <c r="C52">
-        <v>-184.982820621663</v>
+        <v>-206.9858236748206</v>
       </c>
       <c r="D52">
-        <v>486.7171793783369</v>
+        <v>480.0001763251794</v>
       </c>
       <c r="E52">
-        <v>457.4999999999999</v>
+        <v>472.786</v>
       </c>
       <c r="F52">
-        <v>764.3</v>
+        <v>779.586</v>
       </c>
       <c r="G52">
         <v>92.59999999999999</v>
@@ -5807,37 +5807,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M52">
-        <v>180.22194</v>
+        <v>183.8263788</v>
       </c>
       <c r="N52">
-        <v>-138.62194</v>
+        <v>-142.2263788</v>
       </c>
       <c r="O52">
-        <v>-36.7348141</v>
+        <v>-37.689990382</v>
       </c>
       <c r="P52">
-        <v>-101.8871259</v>
+        <v>-104.536388418</v>
       </c>
       <c r="Q52">
-        <v>-22.6871259</v>
+        <v>-25.33638841800001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1258053914239776</v>
+        <v>0.1274381545142629</v>
       </c>
       <c r="T52">
-        <v>1.847699570992554</v>
+        <v>1.885407725502606</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06116902303903731</v>
+        <v>0.05996963043042873</v>
       </c>
       <c r="W52">
-        <v>0.221376344367395</v>
+        <v>0.2216591611445049</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.230826502034103</v>
+        <v>0.226300492190297</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1754908678956863</v>
+        <v>0.1773908678956863</v>
       </c>
       <c r="C53">
-        <v>-206.9858236748206</v>
+        <v>-228.8059527738724</v>
       </c>
       <c r="D53">
-        <v>480.0001763251794</v>
+        <v>473.4660472261276</v>
       </c>
       <c r="E53">
-        <v>472.786</v>
+        <v>488.0719999999999</v>
       </c>
       <c r="F53">
-        <v>779.586</v>
+        <v>794.872</v>
       </c>
       <c r="G53">
         <v>92.59999999999999</v>
@@ -5889,37 +5889,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M53">
-        <v>183.8263788</v>
+        <v>187.4308176</v>
       </c>
       <c r="N53">
-        <v>-142.2263788</v>
+        <v>-145.8308176</v>
       </c>
       <c r="O53">
-        <v>-37.689990382</v>
+        <v>-38.64516666400001</v>
       </c>
       <c r="P53">
-        <v>-104.536388418</v>
+        <v>-107.185650936</v>
       </c>
       <c r="Q53">
-        <v>-25.33638841800001</v>
+        <v>-27.985650936</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1274381545142629</v>
+        <v>0.1291389493999766</v>
       </c>
       <c r="T53">
-        <v>1.885407725502606</v>
+        <v>1.924687053117244</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05996963043042873</v>
+        <v>0.05881636830676663</v>
       </c>
       <c r="W53">
-        <v>0.2216591611445049</v>
+        <v>0.2219311003532644</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.226300492190297</v>
+        <v>0.2219485596481759</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1773908678956863</v>
+        <v>0.1792908678956863</v>
       </c>
       <c r="C54">
-        <v>-228.8059527738724</v>
+        <v>-250.4505758804091</v>
       </c>
       <c r="D54">
-        <v>473.4660472261276</v>
+        <v>467.1074241195909</v>
       </c>
       <c r="E54">
-        <v>488.0719999999999</v>
+        <v>503.358</v>
       </c>
       <c r="F54">
-        <v>794.872</v>
+        <v>810.158</v>
       </c>
       <c r="G54">
         <v>92.59999999999999</v>
@@ -5971,37 +5971,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M54">
-        <v>187.4308176</v>
+        <v>191.0352564</v>
       </c>
       <c r="N54">
-        <v>-145.8308176</v>
+        <v>-149.4352564</v>
       </c>
       <c r="O54">
-        <v>-38.64516666400001</v>
+        <v>-39.600342946</v>
       </c>
       <c r="P54">
-        <v>-107.185650936</v>
+        <v>-109.834913454</v>
       </c>
       <c r="Q54">
-        <v>-27.985650936</v>
+        <v>-30.634913454</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1291389493999766</v>
+        <v>0.1309121185361464</v>
       </c>
       <c r="T54">
-        <v>1.924687053117244</v>
+        <v>1.965637841481441</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05881636830676663</v>
+        <v>0.05770662550852575</v>
       </c>
       <c r="W54">
-        <v>0.2219311003532644</v>
+        <v>0.2221927777050896</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2219485596481759</v>
+        <v>0.2177608509755689</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1792908678956863</v>
+        <v>0.1811908678956863</v>
       </c>
       <c r="C55">
-        <v>-250.4505758804091</v>
+        <v>-271.9266703959378</v>
       </c>
       <c r="D55">
-        <v>467.1074241195909</v>
+        <v>460.9173296040622</v>
       </c>
       <c r="E55">
-        <v>503.358</v>
+        <v>518.644</v>
       </c>
       <c r="F55">
-        <v>810.158</v>
+        <v>825.444</v>
       </c>
       <c r="G55">
         <v>92.59999999999999</v>
@@ -6053,37 +6053,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M55">
-        <v>191.0352564</v>
+        <v>194.6396952</v>
       </c>
       <c r="N55">
-        <v>-149.4352564</v>
+        <v>-153.0396952</v>
       </c>
       <c r="O55">
-        <v>-39.600342946</v>
+        <v>-40.55551922800001</v>
       </c>
       <c r="P55">
-        <v>-109.834913454</v>
+        <v>-112.484175972</v>
       </c>
       <c r="Q55">
-        <v>-30.634913454</v>
+        <v>-33.284175972</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1309121185361464</v>
+        <v>0.1327623819825843</v>
       </c>
       <c r="T55">
-        <v>1.965637841481441</v>
+        <v>2.00836909890495</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05770662550852575</v>
+        <v>0.05663798429540492</v>
       </c>
       <c r="W55">
-        <v>0.2221927777050896</v>
+        <v>0.2224447633031435</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2177608509755689</v>
+        <v>0.2137282426241695</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1811908678956863</v>
+        <v>0.1830908678956863</v>
       </c>
       <c r="C56">
-        <v>-271.9266703959378</v>
+        <v>-293.2408487018837</v>
       </c>
       <c r="D56">
-        <v>460.9173296040622</v>
+        <v>454.8891512981163</v>
       </c>
       <c r="E56">
-        <v>518.644</v>
+        <v>533.9300000000001</v>
       </c>
       <c r="F56">
-        <v>825.444</v>
+        <v>840.73</v>
       </c>
       <c r="G56">
         <v>92.59999999999999</v>
@@ -6135,37 +6135,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M56">
-        <v>194.6396952</v>
+        <v>198.244134</v>
       </c>
       <c r="N56">
-        <v>-153.0396952</v>
+        <v>-156.644134</v>
       </c>
       <c r="O56">
-        <v>-40.55551922800001</v>
+        <v>-41.51069551000001</v>
       </c>
       <c r="P56">
-        <v>-112.484175972</v>
+        <v>-115.13343849</v>
       </c>
       <c r="Q56">
-        <v>-33.284175972</v>
+        <v>-35.93343849</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1327623819825843</v>
+        <v>0.1346948793599751</v>
       </c>
       <c r="T56">
-        <v>2.00836909890495</v>
+        <v>2.052999523325061</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05663798429540492</v>
+        <v>0.05560820276276118</v>
       </c>
       <c r="W56">
-        <v>0.2224447633031435</v>
+        <v>0.2226875857885409</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2137282426241695</v>
+        <v>0.2098422745764573</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1830908678956863</v>
+        <v>0.1849908678956863</v>
       </c>
       <c r="C57">
-        <v>-293.2408487018837</v>
+        <v>-314.3993817212911</v>
       </c>
       <c r="D57">
-        <v>454.8891512981163</v>
+        <v>449.016618278709</v>
       </c>
       <c r="E57">
-        <v>533.9300000000001</v>
+        <v>549.2160000000001</v>
       </c>
       <c r="F57">
-        <v>840.73</v>
+        <v>856.0160000000001</v>
       </c>
       <c r="G57">
         <v>92.59999999999999</v>
@@ -6217,37 +6217,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M57">
-        <v>198.244134</v>
+        <v>201.8485728</v>
       </c>
       <c r="N57">
-        <v>-156.644134</v>
+        <v>-160.2485728</v>
       </c>
       <c r="O57">
-        <v>-41.51069551000001</v>
+        <v>-42.46587179200001</v>
       </c>
       <c r="P57">
-        <v>-115.13343849</v>
+        <v>-117.782701008</v>
       </c>
       <c r="Q57">
-        <v>-35.93343849</v>
+        <v>-38.58270100800003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1346948793599751</v>
+        <v>0.1367152175272473</v>
       </c>
       <c r="T57">
-        <v>2.052999523325061</v>
+        <v>2.09965860340063</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05560820276276118</v>
+        <v>0.05461519914199759</v>
       </c>
       <c r="W57">
-        <v>0.2226875857885409</v>
+        <v>0.222921736042317</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2098422745764573</v>
+        <v>0.2060950911018776</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1849908678956863</v>
+        <v>0.1868908678956863</v>
       </c>
       <c r="C58">
-        <v>-314.3993817212911</v>
+        <v>-335.4082206787233</v>
       </c>
       <c r="D58">
-        <v>449.016618278709</v>
+        <v>443.2937793212768</v>
       </c>
       <c r="E58">
-        <v>549.2160000000001</v>
+        <v>564.502</v>
       </c>
       <c r="F58">
-        <v>856.0160000000001</v>
+        <v>871.302</v>
       </c>
       <c r="G58">
         <v>92.59999999999999</v>
@@ -6299,37 +6299,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M58">
-        <v>201.8485728</v>
+        <v>205.4530116</v>
       </c>
       <c r="N58">
-        <v>-160.2485728</v>
+        <v>-163.8530116</v>
       </c>
       <c r="O58">
-        <v>-42.46587179200001</v>
+        <v>-43.42104807400001</v>
       </c>
       <c r="P58">
-        <v>-117.782701008</v>
+        <v>-120.431963526</v>
       </c>
       <c r="Q58">
-        <v>-38.58270100800003</v>
+        <v>-41.23196352600002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1367152175272473</v>
+        <v>0.1388295249116019</v>
       </c>
       <c r="T58">
-        <v>2.09965860340063</v>
+        <v>2.148487873247156</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05461519914199759</v>
+        <v>0.05365703775354148</v>
       </c>
       <c r="W58">
-        <v>0.222921736042317</v>
+        <v>0.2231476704977149</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2060950911018776</v>
+        <v>0.2024793877492131</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1868908678956863</v>
+        <v>0.1887908678956863</v>
       </c>
       <c r="C59">
-        <v>-335.4082206787233</v>
+        <v>-356.2730172170886</v>
       </c>
       <c r="D59">
-        <v>443.2937793212768</v>
+        <v>437.7149827829115</v>
       </c>
       <c r="E59">
-        <v>564.502</v>
+        <v>579.788</v>
       </c>
       <c r="F59">
-        <v>871.302</v>
+        <v>886.5880000000001</v>
       </c>
       <c r="G59">
         <v>92.59999999999999</v>
@@ -6381,37 +6381,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M59">
-        <v>205.4530116</v>
+        <v>209.0574504</v>
       </c>
       <c r="N59">
-        <v>-163.8530116</v>
+        <v>-167.4574504</v>
       </c>
       <c r="O59">
-        <v>-43.42104807400001</v>
+        <v>-44.37622435600001</v>
       </c>
       <c r="P59">
-        <v>-120.431963526</v>
+        <v>-123.081226044</v>
       </c>
       <c r="Q59">
-        <v>-41.23196352600002</v>
+        <v>-43.88122604400002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1388295249116019</v>
+        <v>0.1410445135999734</v>
       </c>
       <c r="T59">
-        <v>2.148487873247156</v>
+        <v>2.199642346419708</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05365703775354148</v>
+        <v>0.05273191641296319</v>
       </c>
       <c r="W59">
-        <v>0.2231476704977149</v>
+        <v>0.2233658141098233</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2024793877492131</v>
+        <v>0.1989883638225026</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1887908678956863</v>
+        <v>0.1906908678956863</v>
       </c>
       <c r="C60">
-        <v>-356.2730172170884</v>
+        <v>-376.9991420143394</v>
       </c>
       <c r="D60">
-        <v>437.7149827829115</v>
+        <v>432.2748579856605</v>
       </c>
       <c r="E60">
-        <v>579.7879999999998</v>
+        <v>595.0739999999998</v>
       </c>
       <c r="F60">
-        <v>886.5879999999999</v>
+        <v>901.8739999999999</v>
       </c>
       <c r="G60">
         <v>92.59999999999999</v>
@@ -6463,37 +6463,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M60">
-        <v>209.0574504</v>
+        <v>212.6618892</v>
       </c>
       <c r="N60">
-        <v>-167.4574504</v>
+        <v>-171.0618892</v>
       </c>
       <c r="O60">
-        <v>-44.37622435599999</v>
+        <v>-45.331400638</v>
       </c>
       <c r="P60">
-        <v>-123.081226044</v>
+        <v>-125.730488562</v>
       </c>
       <c r="Q60">
-        <v>-43.88122604399997</v>
+        <v>-46.530488562</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1410445135999733</v>
+        <v>0.1433675505170459</v>
       </c>
       <c r="T60">
-        <v>2.199642346419707</v>
+        <v>2.253292159747017</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0527319164129632</v>
+        <v>0.05183815511782823</v>
       </c>
       <c r="W60">
-        <v>0.2233658141098233</v>
+        <v>0.2235765630232161</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1989883638225026</v>
+        <v>0.1956156796899178</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1906908678956863</v>
+        <v>0.1925908678956863</v>
       </c>
       <c r="C61">
-        <v>-376.9991420143394</v>
+        <v>-397.5917020289512</v>
       </c>
       <c r="D61">
-        <v>432.2748579856605</v>
+        <v>426.9682979710487</v>
       </c>
       <c r="E61">
-        <v>595.0739999999998</v>
+        <v>610.3599999999999</v>
       </c>
       <c r="F61">
-        <v>901.8739999999999</v>
+        <v>917.16</v>
       </c>
       <c r="G61">
         <v>92.59999999999999</v>
@@ -6545,37 +6545,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M61">
-        <v>212.6618892</v>
+        <v>216.266328</v>
       </c>
       <c r="N61">
-        <v>-171.0618892</v>
+        <v>-174.666328</v>
       </c>
       <c r="O61">
-        <v>-45.331400638</v>
+        <v>-46.28657692</v>
       </c>
       <c r="P61">
-        <v>-125.730488562</v>
+        <v>-128.37975108</v>
       </c>
       <c r="Q61">
-        <v>-46.530488562</v>
+        <v>-49.17975108</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1433675505170459</v>
+        <v>0.145806739279972</v>
       </c>
       <c r="T61">
-        <v>2.253292159747017</v>
+        <v>2.309624463740693</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05183815511782823</v>
+        <v>0.05097418586586443</v>
       </c>
       <c r="W61">
-        <v>0.2235765630232161</v>
+        <v>0.2237802869728292</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1956156796899178</v>
+        <v>0.1923554183617525</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1925908678956863</v>
+        <v>0.1944908678956863</v>
       </c>
       <c r="C62">
-        <v>-397.5917020289512</v>
+        <v>-418.0555564905834</v>
       </c>
       <c r="D62">
-        <v>426.9682979710487</v>
+        <v>421.7904435094165</v>
       </c>
       <c r="E62">
-        <v>610.3599999999999</v>
+        <v>625.646</v>
       </c>
       <c r="F62">
-        <v>917.16</v>
+        <v>932.4459999999999</v>
       </c>
       <c r="G62">
         <v>92.59999999999999</v>
@@ -6627,37 +6627,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M62">
-        <v>216.266328</v>
+        <v>219.8707668</v>
       </c>
       <c r="N62">
-        <v>-174.666328</v>
+        <v>-178.2707668</v>
       </c>
       <c r="O62">
-        <v>-46.28657692</v>
+        <v>-47.241753202</v>
       </c>
       <c r="P62">
-        <v>-128.37975108</v>
+        <v>-131.029013598</v>
       </c>
       <c r="Q62">
-        <v>-49.17975108</v>
+        <v>-51.829013598</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.145806739279972</v>
+        <v>0.1483710146461251</v>
       </c>
       <c r="T62">
-        <v>2.309624463740693</v>
+        <v>2.368845603836608</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05097418586586443</v>
+        <v>0.05013854347462075</v>
       </c>
       <c r="W62">
-        <v>0.2237802869728292</v>
+        <v>0.2239773314486844</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1923554183617525</v>
+        <v>0.1892020508476254</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1944908678956863</v>
+        <v>0.1963908678956863</v>
       </c>
       <c r="C63">
-        <v>-418.0555564905834</v>
+        <v>-438.3953317411667</v>
       </c>
       <c r="D63">
-        <v>421.7904435094165</v>
+        <v>416.7366682588332</v>
       </c>
       <c r="E63">
-        <v>625.646</v>
+        <v>640.932</v>
       </c>
       <c r="F63">
-        <v>932.4459999999999</v>
+        <v>947.732</v>
       </c>
       <c r="G63">
         <v>92.59999999999999</v>
@@ -6709,37 +6709,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M63">
-        <v>219.8707668</v>
+        <v>223.4752056</v>
       </c>
       <c r="N63">
-        <v>-178.2707668</v>
+        <v>-181.8752056</v>
       </c>
       <c r="O63">
-        <v>-47.241753202</v>
+        <v>-48.19692948400001</v>
       </c>
       <c r="P63">
-        <v>-131.029013598</v>
+        <v>-133.678276116</v>
       </c>
       <c r="Q63">
-        <v>-51.829013598</v>
+        <v>-54.478276116</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1483710146461251</v>
+        <v>0.1510702518736547</v>
       </c>
       <c r="T63">
-        <v>2.368845603836608</v>
+        <v>2.431183646042835</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05013854347462075</v>
+        <v>0.04932985728954621</v>
       </c>
       <c r="W63">
-        <v>0.2239773314486844</v>
+        <v>0.224168019651125</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1892020508476254</v>
+        <v>0.1861504048662121</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1963908678956863</v>
+        <v>0.1982908678956863</v>
       </c>
       <c r="C64">
-        <v>-438.3953317411667</v>
+        <v>-458.6154350216921</v>
       </c>
       <c r="D64">
-        <v>416.7366682588332</v>
+        <v>411.8025649783078</v>
       </c>
       <c r="E64">
-        <v>640.932</v>
+        <v>656.2179999999998</v>
       </c>
       <c r="F64">
-        <v>947.732</v>
+        <v>963.0179999999999</v>
       </c>
       <c r="G64">
         <v>92.59999999999999</v>
@@ -6791,37 +6791,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M64">
-        <v>223.4752056</v>
+        <v>227.0796444</v>
       </c>
       <c r="N64">
-        <v>-181.8752056</v>
+        <v>-185.4796444</v>
       </c>
       <c r="O64">
-        <v>-48.19692948400001</v>
+        <v>-49.152105766</v>
       </c>
       <c r="P64">
-        <v>-133.678276116</v>
+        <v>-136.327538634</v>
       </c>
       <c r="Q64">
-        <v>-54.478276116</v>
+        <v>-57.12753863399998</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1510702518736547</v>
+        <v>0.1539153938161859</v>
       </c>
       <c r="T64">
-        <v>2.431183646042835</v>
+        <v>2.4968913121521</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04932985728954621</v>
+        <v>0.04854684368177564</v>
       </c>
       <c r="W64">
-        <v>0.224168019651125</v>
+        <v>0.2243526542598373</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1861504048662121</v>
+        <v>0.1831956365350024</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1982908678956863</v>
+        <v>0.2001908678956863</v>
       </c>
       <c r="C65">
-        <v>-458.6154350216921</v>
+        <v>-478.7200672910589</v>
       </c>
       <c r="D65">
-        <v>411.8025649783078</v>
+        <v>406.9839327089412</v>
       </c>
       <c r="E65">
-        <v>656.2179999999998</v>
+        <v>671.5039999999999</v>
       </c>
       <c r="F65">
-        <v>963.0179999999999</v>
+        <v>978.304</v>
       </c>
       <c r="G65">
         <v>92.59999999999999</v>
@@ -6873,37 +6873,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M65">
-        <v>227.0796444</v>
+        <v>230.6840832</v>
       </c>
       <c r="N65">
-        <v>-185.4796444</v>
+        <v>-189.0840832</v>
       </c>
       <c r="O65">
-        <v>-49.152105766</v>
+        <v>-50.107282048</v>
       </c>
       <c r="P65">
-        <v>-136.327538634</v>
+        <v>-138.976801152</v>
       </c>
       <c r="Q65">
-        <v>-57.12753863399998</v>
+        <v>-59.776801152</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1539153938161859</v>
+        <v>0.1569185991999689</v>
       </c>
       <c r="T65">
-        <v>2.4968913121521</v>
+        <v>2.566249404156326</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04854684368177564</v>
+        <v>0.04778829924924789</v>
       </c>
       <c r="W65">
-        <v>0.2243526542598373</v>
+        <v>0.2245315190370274</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1831956365350024</v>
+        <v>0.1803332047141429</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2001908678956863</v>
+        <v>0.2020908678956863</v>
       </c>
       <c r="C66">
-        <v>-478.7200672910589</v>
+        <v>-498.7132351553457</v>
       </c>
       <c r="D66">
-        <v>406.9839327089412</v>
+        <v>402.2767648446542</v>
       </c>
       <c r="E66">
-        <v>671.5039999999999</v>
+        <v>686.79</v>
       </c>
       <c r="F66">
-        <v>978.304</v>
+        <v>993.5899999999999</v>
       </c>
       <c r="G66">
         <v>92.59999999999999</v>
@@ -6955,37 +6955,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M66">
-        <v>230.6840832</v>
+        <v>234.288522</v>
       </c>
       <c r="N66">
-        <v>-189.0840832</v>
+        <v>-192.688522</v>
       </c>
       <c r="O66">
-        <v>-50.107282048</v>
+        <v>-51.06245833000001</v>
       </c>
       <c r="P66">
-        <v>-138.976801152</v>
+        <v>-141.62606367</v>
       </c>
       <c r="Q66">
-        <v>-59.776801152</v>
+        <v>-62.42606367</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1569185991999689</v>
+        <v>0.160093416319968</v>
       </c>
       <c r="T66">
-        <v>2.566249404156326</v>
+        <v>2.639570815703649</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04778829924924789</v>
+        <v>0.04705309464541332</v>
       </c>
       <c r="W66">
-        <v>0.2245315190370274</v>
+        <v>0.2247048802826115</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1803332047141429</v>
+        <v>0.1775588477185408</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2020908678956863</v>
+        <v>0.2039908678956863</v>
       </c>
       <c r="C67">
-        <v>-498.7132351553457</v>
+        <v>-518.5987619787079</v>
       </c>
       <c r="D67">
-        <v>402.2767648446542</v>
+        <v>397.6772380212921</v>
       </c>
       <c r="E67">
-        <v>686.79</v>
+        <v>702.076</v>
       </c>
       <c r="F67">
-        <v>993.5899999999999</v>
+        <v>1008.876</v>
       </c>
       <c r="G67">
         <v>92.59999999999999</v>
@@ -7037,37 +7037,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M67">
-        <v>234.288522</v>
+        <v>237.8929608</v>
       </c>
       <c r="N67">
-        <v>-192.688522</v>
+        <v>-196.2929608</v>
       </c>
       <c r="O67">
-        <v>-51.06245833000001</v>
+        <v>-52.017634612</v>
       </c>
       <c r="P67">
-        <v>-141.62606367</v>
+        <v>-144.275326188</v>
       </c>
       <c r="Q67">
-        <v>-62.42606367</v>
+        <v>-65.07532618800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.160093416319968</v>
+        <v>0.1634549873882024</v>
       </c>
       <c r="T67">
-        <v>2.639570815703649</v>
+        <v>2.717205251459639</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04705309464541332</v>
+        <v>0.04634016896896765</v>
       </c>
       <c r="W67">
-        <v>0.2247048802826115</v>
+        <v>0.2248729881571174</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1775588477185408</v>
+        <v>0.1748685621470477</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2039908678956863</v>
+        <v>0.2058908678956863</v>
       </c>
       <c r="C68">
-        <v>-518.5987619787079</v>
+        <v>-538.3802982406535</v>
       </c>
       <c r="D68">
-        <v>397.6772380212921</v>
+        <v>393.1817017593465</v>
       </c>
       <c r="E68">
-        <v>702.076</v>
+        <v>717.3620000000001</v>
       </c>
       <c r="F68">
-        <v>1008.876</v>
+        <v>1024.162</v>
       </c>
       <c r="G68">
         <v>92.59999999999999</v>
@@ -7119,37 +7119,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M68">
-        <v>237.8929608</v>
+        <v>241.4973996</v>
       </c>
       <c r="N68">
-        <v>-196.2929608</v>
+        <v>-199.8973996</v>
       </c>
       <c r="O68">
-        <v>-52.017634612</v>
+        <v>-52.97281089400001</v>
       </c>
       <c r="P68">
-        <v>-144.275326188</v>
+        <v>-146.924588706</v>
       </c>
       <c r="Q68">
-        <v>-65.07532618800001</v>
+        <v>-67.72458870600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1634549873882024</v>
+        <v>0.1670202900363297</v>
       </c>
       <c r="T68">
-        <v>2.717205251459639</v>
+        <v>2.799544804534173</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04634016896896765</v>
+        <v>0.04564852465599799</v>
       </c>
       <c r="W68">
-        <v>0.2248729881571174</v>
+        <v>0.2250360778861157</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1748685621470477</v>
+        <v>0.1722585836075395</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2058908678956863</v>
+        <v>0.2077908678956863</v>
       </c>
       <c r="C69">
-        <v>-538.3802982406535</v>
+        <v>-558.0613311986723</v>
       </c>
       <c r="D69">
-        <v>393.1817017593465</v>
+        <v>388.7866688013278</v>
       </c>
       <c r="E69">
-        <v>717.3620000000001</v>
+        <v>732.6480000000001</v>
       </c>
       <c r="F69">
-        <v>1024.162</v>
+        <v>1039.448</v>
       </c>
       <c r="G69">
         <v>92.59999999999999</v>
@@ -7201,37 +7201,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M69">
-        <v>241.4973996</v>
+        <v>245.1018384</v>
       </c>
       <c r="N69">
-        <v>-199.8973996</v>
+        <v>-203.5018384</v>
       </c>
       <c r="O69">
-        <v>-52.97281089400001</v>
+        <v>-53.92798717600001</v>
       </c>
       <c r="P69">
-        <v>-146.924588706</v>
+        <v>-149.573851224</v>
       </c>
       <c r="Q69">
-        <v>-67.72458870600001</v>
+        <v>-70.37385122400001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1670202900363297</v>
+        <v>0.170808424099965</v>
       </c>
       <c r="T69">
-        <v>2.799544804534173</v>
+        <v>2.887030579675866</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04564852465599799</v>
+        <v>0.04497722282282154</v>
       </c>
       <c r="W69">
-        <v>0.2250360778861157</v>
+        <v>0.2251943708583787</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1722585836075395</v>
+        <v>0.1697253691427228</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2077908678956863</v>
+        <v>0.2096908678956863</v>
       </c>
       <c r="C70">
-        <v>-558.0613311986723</v>
+        <v>-577.6451939099669</v>
       </c>
       <c r="D70">
-        <v>388.7866688013278</v>
+        <v>384.488806090033</v>
       </c>
       <c r="E70">
-        <v>732.6480000000001</v>
+        <v>747.934</v>
       </c>
       <c r="F70">
-        <v>1039.448</v>
+        <v>1054.734</v>
       </c>
       <c r="G70">
         <v>92.59999999999999</v>
@@ -7283,37 +7283,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M70">
-        <v>245.1018384</v>
+        <v>248.7062772</v>
       </c>
       <c r="N70">
-        <v>-203.5018384</v>
+        <v>-207.1062772</v>
       </c>
       <c r="O70">
-        <v>-53.92798717600001</v>
+        <v>-54.883163458</v>
       </c>
       <c r="P70">
-        <v>-149.573851224</v>
+        <v>-152.223113742</v>
       </c>
       <c r="Q70">
-        <v>-70.37385122400001</v>
+        <v>-73.02311374200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.170808424099965</v>
+        <v>0.1748409539096413</v>
       </c>
       <c r="T70">
-        <v>2.887030579675866</v>
+        <v>2.980160598375088</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04497722282282154</v>
+        <v>0.04432537901379516</v>
       </c>
       <c r="W70">
-        <v>0.2251943708583787</v>
+        <v>0.2253480756285471</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1697253691427228</v>
+        <v>0.1672655811841326</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2096908678956863</v>
+        <v>0.2115908678956863</v>
       </c>
       <c r="C71">
-        <v>-577.6451939099669</v>
+        <v>-597.1350736613419</v>
       </c>
       <c r="D71">
-        <v>384.488806090033</v>
+        <v>380.2849263386581</v>
       </c>
       <c r="E71">
-        <v>747.934</v>
+        <v>763.22</v>
       </c>
       <c r="F71">
-        <v>1054.734</v>
+        <v>1070.02</v>
       </c>
       <c r="G71">
         <v>92.59999999999999</v>
@@ -7365,37 +7365,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M71">
-        <v>248.7062772</v>
+        <v>252.310716</v>
       </c>
       <c r="N71">
-        <v>-207.1062772</v>
+        <v>-210.710716</v>
       </c>
       <c r="O71">
-        <v>-54.883163458</v>
+        <v>-55.83833974000001</v>
       </c>
       <c r="P71">
-        <v>-152.223113742</v>
+        <v>-154.87237626</v>
       </c>
       <c r="Q71">
-        <v>-73.02311374200001</v>
+        <v>-75.67237626000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1748409539096413</v>
+        <v>0.1791423190399627</v>
       </c>
       <c r="T71">
-        <v>2.980160598375088</v>
+        <v>3.079499284987591</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04432537901379516</v>
+        <v>0.04369215931359807</v>
       </c>
       <c r="W71">
-        <v>0.2253480756285471</v>
+        <v>0.2254973888338536</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1672655811841326</v>
+        <v>0.1648760728815022</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2115908678956863</v>
+        <v>0.2134908678956863</v>
       </c>
       <c r="C72">
-        <v>-597.1350736613419</v>
+        <v>-616.5340198520519</v>
       </c>
       <c r="D72">
-        <v>380.2849263386581</v>
+        <v>376.1719801479481</v>
       </c>
       <c r="E72">
-        <v>763.22</v>
+        <v>778.5060000000001</v>
       </c>
       <c r="F72">
-        <v>1070.02</v>
+        <v>1085.306</v>
       </c>
       <c r="G72">
         <v>92.59999999999999</v>
@@ -7447,37 +7447,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M72">
-        <v>252.310716</v>
+        <v>255.9151548</v>
       </c>
       <c r="N72">
-        <v>-210.710716</v>
+        <v>-214.3151548</v>
       </c>
       <c r="O72">
-        <v>-55.83833974000001</v>
+        <v>-56.79351602200001</v>
       </c>
       <c r="P72">
-        <v>-154.87237626</v>
+        <v>-157.521638778</v>
       </c>
       <c r="Q72">
-        <v>-75.67237626000001</v>
+        <v>-78.32163877800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1791423190399627</v>
+        <v>0.1837403300413407</v>
       </c>
       <c r="T72">
-        <v>3.079499284987591</v>
+        <v>3.185688915504405</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04369215931359807</v>
+        <v>0.04307677678805445</v>
       </c>
       <c r="W72">
-        <v>0.2254973888338536</v>
+        <v>0.2256424960333768</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1648760728815022</v>
+        <v>0.1625538746719035</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2134908678956863</v>
+        <v>0.2153908678956863</v>
       </c>
       <c r="C73">
-        <v>-616.5340198520516</v>
+        <v>-635.8449513705868</v>
       </c>
       <c r="D73">
-        <v>376.1719801479481</v>
+        <v>372.147048629413</v>
       </c>
       <c r="E73">
-        <v>778.5059999999999</v>
+        <v>793.7919999999999</v>
       </c>
       <c r="F73">
-        <v>1085.306</v>
+        <v>1100.592</v>
       </c>
       <c r="G73">
         <v>92.59999999999999</v>
@@ -7529,37 +7529,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M73">
-        <v>255.9151548</v>
+        <v>259.5195936</v>
       </c>
       <c r="N73">
-        <v>-214.3151548</v>
+        <v>-217.9195936</v>
       </c>
       <c r="O73">
-        <v>-56.79351602199999</v>
+        <v>-57.74869230400001</v>
       </c>
       <c r="P73">
-        <v>-157.521638778</v>
+        <v>-160.170901296</v>
       </c>
       <c r="Q73">
-        <v>-78.32163877799995</v>
+        <v>-80.97090129600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1837403300413407</v>
+        <v>0.18866677039996</v>
       </c>
       <c r="T73">
-        <v>3.185688915504404</v>
+        <v>3.299463519629561</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04307677678805445</v>
+        <v>0.04247848822155368</v>
       </c>
       <c r="W73">
-        <v>0.2256424960333768</v>
+        <v>0.2257835724773577</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1625538746719035</v>
+        <v>0.1602961819681271</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2153908678956863</v>
+        <v>0.2172908678956863</v>
       </c>
       <c r="C74">
-        <v>-635.8449513705868</v>
+        <v>-655.0706635028944</v>
       </c>
       <c r="D74">
-        <v>372.147048629413</v>
+        <v>368.2073364971055</v>
       </c>
       <c r="E74">
-        <v>793.7919999999999</v>
+        <v>809.078</v>
       </c>
       <c r="F74">
-        <v>1100.592</v>
+        <v>1115.878</v>
       </c>
       <c r="G74">
         <v>92.59999999999999</v>
@@ -7611,37 +7611,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M74">
-        <v>259.5195936</v>
+        <v>263.1240324</v>
       </c>
       <c r="N74">
-        <v>-217.9195936</v>
+        <v>-221.5240324</v>
       </c>
       <c r="O74">
-        <v>-57.74869230400001</v>
+        <v>-58.703868586</v>
       </c>
       <c r="P74">
-        <v>-160.170901296</v>
+        <v>-162.820163814</v>
       </c>
       <c r="Q74">
-        <v>-80.97090129600001</v>
+        <v>-83.62016381399998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.18866677039996</v>
+        <v>0.1939581322666251</v>
       </c>
       <c r="T74">
-        <v>3.299463519629561</v>
+        <v>3.421665872208433</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04247848822155368</v>
+        <v>0.0418965911226283</v>
       </c>
       <c r="W74">
-        <v>0.2257835724773577</v>
+        <v>0.2259207838132843</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1602961819681271</v>
+        <v>0.1581003438589746</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2172908678956863</v>
+        <v>0.2191908678956863</v>
       </c>
       <c r="C75">
-        <v>-655.0706635028944</v>
+        <v>-674.2138344063964</v>
       </c>
       <c r="D75">
-        <v>368.2073364971055</v>
+        <v>364.3501655936037</v>
       </c>
       <c r="E75">
-        <v>809.078</v>
+        <v>824.364</v>
       </c>
       <c r="F75">
-        <v>1115.878</v>
+        <v>1131.164</v>
       </c>
       <c r="G75">
         <v>92.59999999999999</v>
@@ -7693,37 +7693,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M75">
-        <v>263.1240324</v>
+        <v>266.7284712</v>
       </c>
       <c r="N75">
-        <v>-221.5240324</v>
+        <v>-225.1284712</v>
       </c>
       <c r="O75">
-        <v>-58.703868586</v>
+        <v>-59.659044868</v>
       </c>
       <c r="P75">
-        <v>-162.820163814</v>
+        <v>-165.469426332</v>
       </c>
       <c r="Q75">
-        <v>-83.62016381399998</v>
+        <v>-86.26942633200001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1939581322666251</v>
+        <v>0.1996565219691877</v>
       </c>
       <c r="T75">
-        <v>3.421665872208433</v>
+        <v>3.553268405754912</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0418965911226283</v>
+        <v>0.0413304209723225</v>
       </c>
       <c r="W75">
-        <v>0.2259207838132843</v>
+        <v>0.2260542867347264</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1581003438589746</v>
+        <v>0.1559638527257453</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2191908678956863</v>
+        <v>0.2210908678956863</v>
       </c>
       <c r="C76">
-        <v>-674.2138344063964</v>
+        <v>-693.2770311813105</v>
       </c>
       <c r="D76">
-        <v>364.3501655936037</v>
+        <v>360.5729688186893</v>
       </c>
       <c r="E76">
-        <v>824.364</v>
+        <v>839.6499999999999</v>
       </c>
       <c r="F76">
-        <v>1131.164</v>
+        <v>1146.45</v>
       </c>
       <c r="G76">
         <v>92.59999999999999</v>
@@ -7775,37 +7775,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M76">
-        <v>266.7284712</v>
+        <v>270.33291</v>
       </c>
       <c r="N76">
-        <v>-225.1284712</v>
+        <v>-228.73291</v>
       </c>
       <c r="O76">
-        <v>-59.659044868</v>
+        <v>-60.61422115</v>
       </c>
       <c r="P76">
-        <v>-165.469426332</v>
+        <v>-168.11868885</v>
       </c>
       <c r="Q76">
-        <v>-86.26942633200001</v>
+        <v>-88.91868884999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1996565219691877</v>
+        <v>0.2058107828479552</v>
       </c>
       <c r="T76">
-        <v>3.553268405754912</v>
+        <v>3.695399141985108</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0413304209723225</v>
+        <v>0.04077934869269154</v>
       </c>
       <c r="W76">
-        <v>0.2260542867347264</v>
+        <v>0.2261842295782633</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1559638527257453</v>
+        <v>0.153884334689402</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2210908678956863</v>
+        <v>0.2229908678956863</v>
       </c>
       <c r="C77">
-        <v>-693.2770311813105</v>
+        <v>-712.2627155682045</v>
       </c>
       <c r="D77">
-        <v>360.5729688186893</v>
+        <v>356.8732844317954</v>
       </c>
       <c r="E77">
-        <v>839.6499999999999</v>
+        <v>854.9359999999999</v>
       </c>
       <c r="F77">
-        <v>1146.45</v>
+        <v>1161.736</v>
       </c>
       <c r="G77">
         <v>92.59999999999999</v>
@@ -7857,37 +7857,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M77">
-        <v>270.33291</v>
+        <v>273.9373488</v>
       </c>
       <c r="N77">
-        <v>-228.73291</v>
+        <v>-232.3373488</v>
       </c>
       <c r="O77">
-        <v>-60.61422115</v>
+        <v>-61.569397432</v>
       </c>
       <c r="P77">
-        <v>-168.11868885</v>
+        <v>-170.767951368</v>
       </c>
       <c r="Q77">
-        <v>-88.91868884999998</v>
+        <v>-91.56795136800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2058107828479552</v>
+        <v>0.2124778987999533</v>
       </c>
       <c r="T77">
-        <v>3.695399141985108</v>
+        <v>3.849374106234488</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04077934869269154</v>
+        <v>0.04024277831515612</v>
       </c>
       <c r="W77">
-        <v>0.2261842295782633</v>
+        <v>0.2263107528732862</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.153884334689402</v>
+        <v>0.1518595408119099</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2229908678956863</v>
+        <v>0.2248908678956863</v>
       </c>
       <c r="C78">
-        <v>-712.2627155682045</v>
+        <v>-731.1732492983463</v>
       </c>
       <c r="D78">
-        <v>356.8732844317954</v>
+        <v>353.2487507016536</v>
       </c>
       <c r="E78">
-        <v>854.9359999999999</v>
+        <v>870.222</v>
       </c>
       <c r="F78">
-        <v>1161.736</v>
+        <v>1177.022</v>
       </c>
       <c r="G78">
         <v>92.59999999999999</v>
@@ -7939,37 +7939,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M78">
-        <v>273.9373488</v>
+        <v>277.5417876</v>
       </c>
       <c r="N78">
-        <v>-232.3373488</v>
+        <v>-235.9417876</v>
       </c>
       <c r="O78">
-        <v>-61.569397432</v>
+        <v>-62.52457371400001</v>
       </c>
       <c r="P78">
-        <v>-170.767951368</v>
+        <v>-173.417213886</v>
       </c>
       <c r="Q78">
-        <v>-91.56795136800001</v>
+        <v>-94.21721388600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2124778987999533</v>
+        <v>0.2197247639651687</v>
       </c>
       <c r="T78">
-        <v>3.849374106234488</v>
+        <v>4.0167381978099</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04024277831515612</v>
+        <v>0.0397201448305437</v>
       </c>
       <c r="W78">
-        <v>0.2263107528732862</v>
+        <v>0.2264339898489578</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1518595408119099</v>
+        <v>0.1498873389831837</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2248908678956863</v>
+        <v>0.2267908678956863</v>
       </c>
       <c r="C79">
-        <v>-731.1732492983463</v>
+        <v>-750.010899121296</v>
       </c>
       <c r="D79">
-        <v>353.2487507016536</v>
+        <v>349.697100878704</v>
       </c>
       <c r="E79">
-        <v>870.222</v>
+        <v>885.508</v>
       </c>
       <c r="F79">
-        <v>1177.022</v>
+        <v>1192.308</v>
       </c>
       <c r="G79">
         <v>92.59999999999999</v>
@@ -8021,37 +8021,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M79">
-        <v>277.5417876</v>
+        <v>281.1462264</v>
       </c>
       <c r="N79">
-        <v>-235.9417876</v>
+        <v>-239.5462264</v>
       </c>
       <c r="O79">
-        <v>-62.52457371400001</v>
+        <v>-63.479749996</v>
       </c>
       <c r="P79">
-        <v>-173.417213886</v>
+        <v>-176.066476404</v>
       </c>
       <c r="Q79">
-        <v>-94.21721388600001</v>
+        <v>-96.86647640399998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2197247639651687</v>
+        <v>0.2276304350544945</v>
       </c>
       <c r="T79">
-        <v>4.0167381978099</v>
+        <v>4.199317206801259</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0397201448305437</v>
+        <v>0.0392109122045111</v>
       </c>
       <c r="W79">
-        <v>0.2264339898489578</v>
+        <v>0.2265540669021763</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1498873389831837</v>
+        <v>0.1479657064321174</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2267908678956863</v>
+        <v>0.2286908678956863</v>
       </c>
       <c r="C80">
-        <v>-750.010899121296</v>
+        <v>-768.7778415322233</v>
       </c>
       <c r="D80">
-        <v>349.697100878704</v>
+        <v>346.2161584677767</v>
       </c>
       <c r="E80">
-        <v>885.508</v>
+        <v>900.7940000000001</v>
       </c>
       <c r="F80">
-        <v>1192.308</v>
+        <v>1207.594</v>
       </c>
       <c r="G80">
         <v>92.59999999999999</v>
@@ -8103,37 +8103,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M80">
-        <v>281.1462264</v>
+        <v>284.7506652</v>
       </c>
       <c r="N80">
-        <v>-239.5462264</v>
+        <v>-243.1506652</v>
       </c>
       <c r="O80">
-        <v>-63.479749996</v>
+        <v>-64.43492627800001</v>
       </c>
       <c r="P80">
-        <v>-176.066476404</v>
+        <v>-178.715738922</v>
       </c>
       <c r="Q80">
-        <v>-96.86647640399998</v>
+        <v>-99.51573892200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2276304350544945</v>
+        <v>0.2362890271999467</v>
       </c>
       <c r="T80">
-        <v>4.199317206801259</v>
+        <v>4.399284692839416</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0392109122045111</v>
+        <v>0.0387145715436945</v>
       </c>
       <c r="W80">
-        <v>0.2265540669021763</v>
+        <v>0.2266711040299969</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1479657064321174</v>
+        <v>0.1460927228063943</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2286908678956863</v>
+        <v>0.2305908678956863</v>
       </c>
       <c r="C81">
-        <v>-768.7778415322233</v>
+        <v>-787.4761672196681</v>
       </c>
       <c r="D81">
-        <v>346.2161584677767</v>
+        <v>342.8038327803318</v>
       </c>
       <c r="E81">
-        <v>900.7940000000001</v>
+        <v>916.0799999999999</v>
       </c>
       <c r="F81">
-        <v>1207.594</v>
+        <v>1222.88</v>
       </c>
       <c r="G81">
         <v>92.59999999999999</v>
@@ -8185,37 +8185,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M81">
-        <v>284.7506652</v>
+        <v>288.355104</v>
       </c>
       <c r="N81">
-        <v>-243.1506652</v>
+        <v>-246.755104</v>
       </c>
       <c r="O81">
-        <v>-64.43492627800001</v>
+        <v>-65.39010256</v>
       </c>
       <c r="P81">
-        <v>-178.715738922</v>
+        <v>-181.36500144</v>
       </c>
       <c r="Q81">
-        <v>-99.51573892200001</v>
+        <v>-102.16500144</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2362890271999467</v>
+        <v>0.245813478559944</v>
       </c>
       <c r="T81">
-        <v>4.399284692839416</v>
+        <v>4.619248927481387</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0387145715436945</v>
+        <v>0.03823063939939832</v>
       </c>
       <c r="W81">
-        <v>0.2266711040299969</v>
+        <v>0.2267852152296219</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1460927228063943</v>
+        <v>0.1442665637713144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2305908678956863</v>
+        <v>0.2324908678956863</v>
       </c>
       <c r="C82">
-        <v>-787.4761672196681</v>
+        <v>-806.1078852528464</v>
       </c>
       <c r="D82">
-        <v>342.8038327803318</v>
+        <v>339.4581147471536</v>
       </c>
       <c r="E82">
-        <v>916.0799999999999</v>
+        <v>931.366</v>
       </c>
       <c r="F82">
-        <v>1222.88</v>
+        <v>1238.166</v>
       </c>
       <c r="G82">
         <v>92.59999999999999</v>
@@ -8267,37 +8267,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M82">
-        <v>288.355104</v>
+        <v>291.9595428</v>
       </c>
       <c r="N82">
-        <v>-246.755104</v>
+        <v>-250.3595428</v>
       </c>
       <c r="O82">
-        <v>-65.39010256</v>
+        <v>-66.34527884200001</v>
       </c>
       <c r="P82">
-        <v>-181.36500144</v>
+        <v>-184.014263958</v>
       </c>
       <c r="Q82">
-        <v>-102.16500144</v>
+        <v>-104.814263958</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.245813478559944</v>
+        <v>0.2563405037473095</v>
       </c>
       <c r="T82">
-        <v>4.619248927481387</v>
+        <v>4.86236729208567</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03823063939939832</v>
+        <v>0.03775865619693661</v>
       </c>
       <c r="W82">
-        <v>0.2267852152296219</v>
+        <v>0.2268965088687624</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1442665637713144</v>
+        <v>0.1424854950827796</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2324908678956863</v>
+        <v>0.2343908678956863</v>
       </c>
       <c r="C83">
-        <v>-806.1078852528464</v>
+        <v>-824.6749270261178</v>
       </c>
       <c r="D83">
-        <v>339.4581147471536</v>
+        <v>336.1770729738823</v>
       </c>
       <c r="E83">
-        <v>931.366</v>
+        <v>946.652</v>
       </c>
       <c r="F83">
-        <v>1238.166</v>
+        <v>1253.452</v>
       </c>
       <c r="G83">
         <v>92.59999999999999</v>
@@ -8349,37 +8349,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M83">
-        <v>291.9595428</v>
+        <v>295.5639816</v>
       </c>
       <c r="N83">
-        <v>-250.3595428</v>
+        <v>-253.9639816</v>
       </c>
       <c r="O83">
-        <v>-66.34527884200001</v>
+        <v>-67.30045512400001</v>
       </c>
       <c r="P83">
-        <v>-184.014263958</v>
+        <v>-186.663526476</v>
       </c>
       <c r="Q83">
-        <v>-104.814263958</v>
+        <v>-107.463526476</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2563405037473095</v>
+        <v>0.2680371983999378</v>
       </c>
       <c r="T83">
-        <v>4.86236729208567</v>
+        <v>5.132498808312652</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03775865619693661</v>
+        <v>0.03729818477990079</v>
       </c>
       <c r="W83">
-        <v>0.2268965088687624</v>
+        <v>0.2270050880288994</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1424854950827796</v>
+        <v>0.1407478670939653</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2343908678956863</v>
+        <v>0.2362908678956863</v>
       </c>
       <c r="C84">
-        <v>-824.6749270261178</v>
+        <v>-843.1791499768931</v>
       </c>
       <c r="D84">
-        <v>336.1770729738823</v>
+        <v>332.9588500231069</v>
       </c>
       <c r="E84">
-        <v>946.652</v>
+        <v>961.9380000000001</v>
       </c>
       <c r="F84">
-        <v>1253.452</v>
+        <v>1268.738</v>
       </c>
       <c r="G84">
         <v>92.59999999999999</v>
@@ -8431,37 +8431,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M84">
-        <v>295.5639816</v>
+        <v>299.1684204</v>
       </c>
       <c r="N84">
-        <v>-253.9639816</v>
+        <v>-257.5684204</v>
       </c>
       <c r="O84">
-        <v>-67.30045512400001</v>
+        <v>-68.25563140600001</v>
       </c>
       <c r="P84">
-        <v>-186.663526476</v>
+        <v>-189.312788994</v>
       </c>
       <c r="Q84">
-        <v>-107.463526476</v>
+        <v>-110.112788994</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2680371983999378</v>
+        <v>0.2811099747764048</v>
       </c>
       <c r="T84">
-        <v>5.132498808312652</v>
+        <v>5.434410502919279</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03729818477990079</v>
+        <v>0.03684880905966102</v>
       </c>
       <c r="W84">
-        <v>0.2270050880288994</v>
+        <v>0.2271110508237319</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1407478670939653</v>
+        <v>0.1390521096590981</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2362908678956863</v>
+        <v>0.2381908678956863</v>
       </c>
       <c r="C85">
-        <v>-843.1791499768931</v>
+        <v>-861.6223410920169</v>
       </c>
       <c r="D85">
-        <v>332.9588500231069</v>
+        <v>329.8016589079833</v>
       </c>
       <c r="E85">
-        <v>961.9380000000001</v>
+        <v>977.2240000000002</v>
       </c>
       <c r="F85">
-        <v>1268.738</v>
+        <v>1284.024</v>
       </c>
       <c r="G85">
         <v>92.59999999999999</v>
@@ -8513,37 +8513,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M85">
-        <v>299.1684204</v>
+        <v>302.7728592</v>
       </c>
       <c r="N85">
-        <v>-257.5684204</v>
+        <v>-261.1728592000001</v>
       </c>
       <c r="O85">
-        <v>-68.25563140600001</v>
+        <v>-69.21080768800002</v>
       </c>
       <c r="P85">
-        <v>-189.312788994</v>
+        <v>-191.962051512</v>
       </c>
       <c r="Q85">
-        <v>-110.112788994</v>
+        <v>-112.762051512</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2811099747764048</v>
+        <v>0.2958168481999301</v>
       </c>
       <c r="T85">
-        <v>5.434410502919279</v>
+        <v>5.774061159351735</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03684880905966102</v>
+        <v>0.03641013276133172</v>
       </c>
       <c r="W85">
-        <v>0.2271110508237319</v>
+        <v>0.227214490694878</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1390521096590981</v>
+        <v>0.1373967274012518</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2381908678956863</v>
+        <v>0.2400908678956863</v>
       </c>
       <c r="C86">
-        <v>-861.6223410920167</v>
+        <v>-880.0062202165334</v>
       </c>
       <c r="D86">
-        <v>329.8016589079833</v>
+        <v>326.7037797834666</v>
       </c>
       <c r="E86">
-        <v>977.2239999999999</v>
+        <v>992.51</v>
       </c>
       <c r="F86">
-        <v>1284.024</v>
+        <v>1299.31</v>
       </c>
       <c r="G86">
         <v>92.59999999999999</v>
@@ -8595,37 +8595,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M86">
-        <v>302.7728592</v>
+        <v>306.377298</v>
       </c>
       <c r="N86">
-        <v>-261.1728591999999</v>
+        <v>-264.777298</v>
       </c>
       <c r="O86">
-        <v>-69.21080768799999</v>
+        <v>-70.16598397</v>
       </c>
       <c r="P86">
-        <v>-191.962051512</v>
+        <v>-194.61131403</v>
       </c>
       <c r="Q86">
-        <v>-112.762051512</v>
+        <v>-115.41131403</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2958168481999299</v>
+        <v>0.3124846380799253</v>
       </c>
       <c r="T86">
-        <v>5.774061159351731</v>
+        <v>6.15899856997518</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03641013276133173</v>
+        <v>0.03598177825825724</v>
       </c>
       <c r="W86">
-        <v>0.227214490694878</v>
+        <v>0.227315496686703</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1373967274012519</v>
+        <v>0.1357802953141783</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2400908678956863</v>
+        <v>0.2419908678956863</v>
       </c>
       <c r="C87">
-        <v>-880.0062202165334</v>
+        <v>-898.3324431777114</v>
       </c>
       <c r="D87">
-        <v>326.7037797834666</v>
+        <v>323.6635568222886</v>
       </c>
       <c r="E87">
-        <v>992.51</v>
+        <v>1007.796</v>
       </c>
       <c r="F87">
-        <v>1299.31</v>
+        <v>1314.596</v>
       </c>
       <c r="G87">
         <v>92.59999999999999</v>
@@ -8677,37 +8677,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M87">
-        <v>306.377298</v>
+        <v>309.9817368</v>
       </c>
       <c r="N87">
-        <v>-264.777298</v>
+        <v>-268.3817368</v>
       </c>
       <c r="O87">
-        <v>-70.16598397</v>
+        <v>-71.12116025200001</v>
       </c>
       <c r="P87">
-        <v>-194.61131403</v>
+        <v>-197.260576548</v>
       </c>
       <c r="Q87">
-        <v>-115.41131403</v>
+        <v>-118.060576548</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3124846380799253</v>
+        <v>0.33153354079992</v>
       </c>
       <c r="T87">
-        <v>6.15899856997518</v>
+        <v>6.598927039259122</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03598177825825724</v>
+        <v>0.03556338548781238</v>
       </c>
       <c r="W87">
-        <v>0.227315496686703</v>
+        <v>0.2274141537019738</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1357802953141783</v>
+        <v>0.1342014546709902</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2419908678956863</v>
+        <v>0.2438908678956863</v>
       </c>
       <c r="C88">
-        <v>-898.3324431777114</v>
+        <v>-916.6026047362451</v>
       </c>
       <c r="D88">
-        <v>323.6635568222886</v>
+        <v>320.6793952637548</v>
       </c>
       <c r="E88">
-        <v>1007.796</v>
+        <v>1023.082</v>
       </c>
       <c r="F88">
-        <v>1314.596</v>
+        <v>1329.882</v>
       </c>
       <c r="G88">
         <v>92.59999999999999</v>
@@ -8759,37 +8759,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M88">
-        <v>309.9817368</v>
+        <v>313.5861756</v>
       </c>
       <c r="N88">
-        <v>-268.3817368</v>
+        <v>-271.9861756</v>
       </c>
       <c r="O88">
-        <v>-71.12116025200001</v>
+        <v>-72.07633653400001</v>
       </c>
       <c r="P88">
-        <v>-197.260576548</v>
+        <v>-199.909839066</v>
       </c>
       <c r="Q88">
-        <v>-118.060576548</v>
+        <v>-120.709839066</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.33153354079992</v>
+        <v>0.3535130439383753</v>
       </c>
       <c r="T88">
-        <v>6.598927039259122</v>
+        <v>7.106536811509823</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03556338548781238</v>
+        <v>0.03515461094197547</v>
       </c>
       <c r="W88">
-        <v>0.2274141537019738</v>
+        <v>0.2275105427398822</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1342014546709902</v>
+        <v>0.1326589092150017</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2438908678956863</v>
+        <v>0.2457908678956863</v>
       </c>
       <c r="C89">
-        <v>-916.6026047362451</v>
+        <v>-934.8182413756912</v>
       </c>
       <c r="D89">
-        <v>320.6793952637548</v>
+        <v>317.7497586243087</v>
       </c>
       <c r="E89">
-        <v>1023.082</v>
+        <v>1038.368</v>
       </c>
       <c r="F89">
-        <v>1329.882</v>
+        <v>1345.168</v>
       </c>
       <c r="G89">
         <v>92.59999999999999</v>
@@ -8841,37 +8841,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M89">
-        <v>313.5861756</v>
+        <v>317.1906144</v>
       </c>
       <c r="N89">
-        <v>-271.9861756</v>
+        <v>-275.5906144</v>
       </c>
       <c r="O89">
-        <v>-72.07633653400001</v>
+        <v>-73.03151281600002</v>
       </c>
       <c r="P89">
-        <v>-199.909839066</v>
+        <v>-202.559101584</v>
       </c>
       <c r="Q89">
-        <v>-120.709839066</v>
+        <v>-123.359101584</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3535130439383753</v>
+        <v>0.3791557975999066</v>
       </c>
       <c r="T89">
-        <v>7.106536811509823</v>
+        <v>7.698748212468975</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03515461094197547</v>
+        <v>0.03475512672672574</v>
       </c>
       <c r="W89">
-        <v>0.2275105427398822</v>
+        <v>0.2276047411178381</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1326589092150017</v>
+        <v>0.1311514216102857</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2457908678956863</v>
+        <v>0.2476908678956863</v>
       </c>
       <c r="C90">
-        <v>-934.8182413756912</v>
+        <v>-952.9808339403866</v>
       </c>
       <c r="D90">
-        <v>317.7497586243087</v>
+        <v>314.8731660596134</v>
       </c>
       <c r="E90">
-        <v>1038.368</v>
+        <v>1053.654</v>
       </c>
       <c r="F90">
-        <v>1345.168</v>
+        <v>1360.454</v>
       </c>
       <c r="G90">
         <v>92.59999999999999</v>
@@ -8923,37 +8923,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M90">
-        <v>317.1906144</v>
+        <v>320.7950532</v>
       </c>
       <c r="N90">
-        <v>-275.5906144</v>
+        <v>-279.1950532</v>
       </c>
       <c r="O90">
-        <v>-73.03151281600002</v>
+        <v>-73.986689098</v>
       </c>
       <c r="P90">
-        <v>-202.559101584</v>
+        <v>-205.208364102</v>
       </c>
       <c r="Q90">
-        <v>-123.359101584</v>
+        <v>-126.008364102</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3791557975999066</v>
+        <v>0.4094608701089891</v>
       </c>
       <c r="T90">
-        <v>7.698748212468975</v>
+        <v>8.398634413602519</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03475512672672574</v>
+        <v>0.03436461968485242</v>
       </c>
       <c r="W90">
-        <v>0.2276047411178381</v>
+        <v>0.2276968226783118</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1311514216102857</v>
+        <v>0.1296778101315187</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2476908678956863</v>
+        <v>0.2495908678956863</v>
       </c>
       <c r="C91">
-        <v>-952.9808339403866</v>
+        <v>-971.0918101313648</v>
       </c>
       <c r="D91">
-        <v>314.8731660596134</v>
+        <v>312.0481898686352</v>
       </c>
       <c r="E91">
-        <v>1053.654</v>
+        <v>1068.94</v>
       </c>
       <c r="F91">
-        <v>1360.454</v>
+        <v>1375.74</v>
       </c>
       <c r="G91">
         <v>92.59999999999999</v>
@@ -9005,37 +9005,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M91">
-        <v>320.7950532</v>
+        <v>324.399492</v>
       </c>
       <c r="N91">
-        <v>-279.1950532</v>
+        <v>-282.799492</v>
       </c>
       <c r="O91">
-        <v>-73.986689098</v>
+        <v>-74.94186538</v>
       </c>
       <c r="P91">
-        <v>-205.208364102</v>
+        <v>-207.85762662</v>
       </c>
       <c r="Q91">
-        <v>-126.008364102</v>
+        <v>-128.65762662</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4094608701089891</v>
+        <v>0.4458269571198881</v>
       </c>
       <c r="T91">
-        <v>8.398634413602519</v>
+        <v>9.238497854962773</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03436461968485242</v>
+        <v>0.03398279057724295</v>
       </c>
       <c r="W91">
-        <v>0.2276968226783118</v>
+        <v>0.2277868579818861</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1296778101315187</v>
+        <v>0.1282369455745017</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2495908678956863</v>
+        <v>0.2514908678956863</v>
       </c>
       <c r="C92">
-        <v>-971.0918101313648</v>
+        <v>-989.1525468691119</v>
       </c>
       <c r="D92">
-        <v>312.0481898686352</v>
+        <v>309.2734531308882</v>
       </c>
       <c r="E92">
-        <v>1068.94</v>
+        <v>1084.226</v>
       </c>
       <c r="F92">
-        <v>1375.74</v>
+        <v>1391.026</v>
       </c>
       <c r="G92">
         <v>92.59999999999999</v>
@@ -9087,37 +9087,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M92">
-        <v>324.399492</v>
+        <v>328.0039308</v>
       </c>
       <c r="N92">
-        <v>-282.799492</v>
+        <v>-286.4039308</v>
       </c>
       <c r="O92">
-        <v>-74.94186538</v>
+        <v>-75.89704166200001</v>
       </c>
       <c r="P92">
-        <v>-207.85762662</v>
+        <v>-210.506889138</v>
       </c>
       <c r="Q92">
-        <v>-128.65762662</v>
+        <v>-131.306889138</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4458269571198881</v>
+        <v>0.4902743967998757</v>
       </c>
       <c r="T92">
-        <v>9.238497854962773</v>
+        <v>10.2649976166253</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03398279057724295</v>
+        <v>0.03360935331815236</v>
       </c>
       <c r="W92">
-        <v>0.2277868579818861</v>
+        <v>0.2278749144875797</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1282369455745017</v>
+        <v>0.1268277483703864</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2514908678956863</v>
+        <v>0.2533908678956863</v>
       </c>
       <c r="C93">
-        <v>-989.1525468691119</v>
+        <v>-1007.164372531374</v>
       </c>
       <c r="D93">
-        <v>309.2734531308882</v>
+        <v>306.5476274686258</v>
       </c>
       <c r="E93">
-        <v>1084.226</v>
+        <v>1099.512</v>
       </c>
       <c r="F93">
-        <v>1391.026</v>
+        <v>1406.312</v>
       </c>
       <c r="G93">
         <v>92.59999999999999</v>
@@ -9169,37 +9169,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M93">
-        <v>328.0039308</v>
+        <v>331.6083696</v>
       </c>
       <c r="N93">
-        <v>-286.4039308</v>
+        <v>-290.0083696</v>
       </c>
       <c r="O93">
-        <v>-75.89704166200001</v>
+        <v>-76.85221794400002</v>
       </c>
       <c r="P93">
-        <v>-210.506889138</v>
+        <v>-213.156151656</v>
       </c>
       <c r="Q93">
-        <v>-131.306889138</v>
+        <v>-133.956151656</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4902743967998757</v>
+        <v>0.5458336963998602</v>
       </c>
       <c r="T93">
-        <v>10.2649976166253</v>
+        <v>11.54812231870347</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03360935331815236</v>
+        <v>0.03324403426034636</v>
       </c>
       <c r="W93">
-        <v>0.2278749144875797</v>
+        <v>0.2279610567214103</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1268277483703864</v>
+        <v>0.1254491858880994</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2533908678956863</v>
+        <v>0.2552908678956863</v>
       </c>
       <c r="C94">
-        <v>-1007.164372531374</v>
+        <v>-1025.12856907366</v>
       </c>
       <c r="D94">
-        <v>306.5476274686258</v>
+        <v>303.8694309263397</v>
       </c>
       <c r="E94">
-        <v>1099.512</v>
+        <v>1114.798</v>
       </c>
       <c r="F94">
-        <v>1406.312</v>
+        <v>1421.598</v>
       </c>
       <c r="G94">
         <v>92.59999999999999</v>
@@ -9251,37 +9251,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M94">
-        <v>331.6083696</v>
+        <v>335.2128084</v>
       </c>
       <c r="N94">
-        <v>-290.0083696</v>
+        <v>-293.6128084000001</v>
       </c>
       <c r="O94">
-        <v>-76.85221794400002</v>
+        <v>-77.80739422600001</v>
       </c>
       <c r="P94">
-        <v>-213.156151656</v>
+        <v>-215.805414174</v>
       </c>
       <c r="Q94">
-        <v>-133.956151656</v>
+        <v>-136.605414174</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5458336963998602</v>
+        <v>0.6172670815998402</v>
       </c>
       <c r="T94">
-        <v>11.54812231870347</v>
+        <v>13.19785407851825</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03324403426034636</v>
+        <v>0.03288657152636414</v>
       </c>
       <c r="W94">
-        <v>0.2279610567214103</v>
+        <v>0.2280453464340834</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1254491858880994</v>
+        <v>0.124100269910808</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2552908678956863</v>
+        <v>0.2571908678956863</v>
       </c>
       <c r="C95">
-        <v>-1025.12856907366</v>
+        <v>-1043.04637403955</v>
       </c>
       <c r="D95">
-        <v>303.8694309263397</v>
+        <v>301.2376259604496</v>
       </c>
       <c r="E95">
-        <v>1114.798</v>
+        <v>1130.084</v>
       </c>
       <c r="F95">
-        <v>1421.598</v>
+        <v>1436.884</v>
       </c>
       <c r="G95">
         <v>92.59999999999999</v>
@@ -9333,37 +9333,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M95">
-        <v>335.2128084</v>
+        <v>338.8172472</v>
       </c>
       <c r="N95">
-        <v>-293.6128084000001</v>
+        <v>-297.2172472</v>
       </c>
       <c r="O95">
-        <v>-77.80739422600001</v>
+        <v>-78.762570508</v>
       </c>
       <c r="P95">
-        <v>-215.805414174</v>
+        <v>-218.454676692</v>
       </c>
       <c r="Q95">
-        <v>-136.605414174</v>
+        <v>-139.254676692</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6172670815998402</v>
+        <v>0.7125115951998138</v>
       </c>
       <c r="T95">
-        <v>13.19785407851825</v>
+        <v>15.39749642493796</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03288657152636414</v>
+        <v>0.03253671438246665</v>
       </c>
       <c r="W95">
-        <v>0.2280453464340834</v>
+        <v>0.2281278427486144</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.124100269910808</v>
+        <v>0.1227800542734592</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2571908678956863</v>
+        <v>0.2590908678956864</v>
       </c>
       <c r="C96">
-        <v>-1043.04637403955</v>
+        <v>-1060.918982467434</v>
       </c>
       <c r="D96">
-        <v>301.2376259604496</v>
+        <v>298.6510175325657</v>
       </c>
       <c r="E96">
-        <v>1130.084</v>
+        <v>1145.37</v>
       </c>
       <c r="F96">
-        <v>1436.884</v>
+        <v>1452.17</v>
       </c>
       <c r="G96">
         <v>92.59999999999999</v>
@@ -9415,37 +9415,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M96">
-        <v>338.8172472</v>
+        <v>342.421686</v>
       </c>
       <c r="N96">
-        <v>-297.2172472</v>
+        <v>-300.821686</v>
       </c>
       <c r="O96">
-        <v>-78.762570508</v>
+        <v>-79.71774679000001</v>
       </c>
       <c r="P96">
-        <v>-218.454676692</v>
+        <v>-221.10393921</v>
       </c>
       <c r="Q96">
-        <v>-139.254676692</v>
+        <v>-141.90393921</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7125115951998138</v>
+        <v>0.845853914239777</v>
       </c>
       <c r="T96">
-        <v>15.39749642493796</v>
+        <v>18.47699570992557</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03253671438246665</v>
+        <v>0.0321942226521249</v>
       </c>
       <c r="W96">
-        <v>0.2281278427486144</v>
+        <v>0.228208602298629</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1227800542734592</v>
+        <v>0.121487632649528</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2590908678956864</v>
+        <v>0.2609908678956863</v>
       </c>
       <c r="C97">
-        <v>-1060.918982467434</v>
+        <v>-1078.747548699852</v>
       </c>
       <c r="D97">
-        <v>298.6510175325657</v>
+        <v>296.1084513001484</v>
       </c>
       <c r="E97">
-        <v>1145.37</v>
+        <v>1160.656</v>
       </c>
       <c r="F97">
-        <v>1452.17</v>
+        <v>1467.456</v>
       </c>
       <c r="G97">
         <v>92.59999999999999</v>
@@ -9497,37 +9497,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M97">
-        <v>342.421686</v>
+        <v>346.0261248</v>
       </c>
       <c r="N97">
-        <v>-300.821686</v>
+        <v>-304.4261248</v>
       </c>
       <c r="O97">
-        <v>-79.71774679000001</v>
+        <v>-80.67292307200002</v>
       </c>
       <c r="P97">
-        <v>-221.10393921</v>
+        <v>-223.753201728</v>
       </c>
       <c r="Q97">
-        <v>-141.90393921</v>
+        <v>-144.553201728</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.845853914239777</v>
+        <v>1.045867392799722</v>
       </c>
       <c r="T97">
-        <v>18.47699570992557</v>
+        <v>23.09624463740697</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0321942226521249</v>
+        <v>0.03185886616616526</v>
       </c>
       <c r="W97">
-        <v>0.228208602298629</v>
+        <v>0.2282876793580182</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.121487632649528</v>
+        <v>0.1202221364760954</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2609908678956863</v>
+        <v>0.2628908678956863</v>
       </c>
       <c r="C98">
-        <v>-1078.747548699851</v>
+        <v>-1096.533188101189</v>
       </c>
       <c r="D98">
-        <v>296.1084513001484</v>
+        <v>293.6088118988105</v>
       </c>
       <c r="E98">
-        <v>1160.656</v>
+        <v>1175.942</v>
       </c>
       <c r="F98">
-        <v>1467.456</v>
+        <v>1482.742</v>
       </c>
       <c r="G98">
         <v>92.59999999999999</v>
@@ -9579,37 +9579,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M98">
-        <v>346.0261248</v>
+        <v>349.6305636</v>
       </c>
       <c r="N98">
-        <v>-304.4261248</v>
+        <v>-308.0305636000001</v>
       </c>
       <c r="O98">
-        <v>-80.67292307200002</v>
+        <v>-81.62809935400001</v>
       </c>
       <c r="P98">
-        <v>-223.753201728</v>
+        <v>-226.402464246</v>
       </c>
       <c r="Q98">
-        <v>-144.553201728</v>
+        <v>-147.202464246</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.045867392799719</v>
+        <v>1.379223190399626</v>
       </c>
       <c r="T98">
-        <v>23.0962446374069</v>
+        <v>30.79499284987588</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03185886616616527</v>
+        <v>0.03153042424692645</v>
       </c>
       <c r="W98">
-        <v>0.2282876793580182</v>
+        <v>0.2283651259625748</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1202221364760953</v>
+        <v>0.1189827330072695</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2628908678956863</v>
+        <v>0.2647908678956863</v>
       </c>
       <c r="C99">
-        <v>-1096.533188101189</v>
+        <v>-1114.276978689107</v>
       </c>
       <c r="D99">
-        <v>293.6088118988105</v>
+        <v>291.1510213108924</v>
       </c>
       <c r="E99">
-        <v>1175.942</v>
+        <v>1191.228</v>
       </c>
       <c r="F99">
-        <v>1482.742</v>
+        <v>1498.028</v>
       </c>
       <c r="G99">
         <v>92.59999999999999</v>
@@ -9661,37 +9661,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M99">
-        <v>349.6305636</v>
+        <v>353.2350024</v>
       </c>
       <c r="N99">
-        <v>-308.0305636000001</v>
+        <v>-311.6350024</v>
       </c>
       <c r="O99">
-        <v>-81.62809935400001</v>
+        <v>-82.583275636</v>
       </c>
       <c r="P99">
-        <v>-226.402464246</v>
+        <v>-229.051726764</v>
       </c>
       <c r="Q99">
-        <v>-147.202464246</v>
+        <v>-149.851726764</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.379223190399626</v>
+        <v>2.045934785599438</v>
       </c>
       <c r="T99">
-        <v>30.79499284987588</v>
+        <v>46.19248927481381</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03153042424692645</v>
+        <v>0.03120868522399863</v>
       </c>
       <c r="W99">
-        <v>0.2283651259625748</v>
+        <v>0.2284409920241811</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1189827330072695</v>
+        <v>0.1177686234867873</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2647908678956863</v>
+        <v>0.2666908678956863</v>
       </c>
       <c r="C100">
-        <v>-1114.276978689107</v>
+        <v>-1131.979962684703</v>
       </c>
       <c r="D100">
-        <v>291.1510213108924</v>
+        <v>288.7340373152973</v>
       </c>
       <c r="E100">
-        <v>1191.228</v>
+        <v>1206.514</v>
       </c>
       <c r="F100">
-        <v>1498.028</v>
+        <v>1513.314</v>
       </c>
       <c r="G100">
         <v>92.59999999999999</v>
@@ -9743,37 +9743,37 @@
         <v>41.59999999999999</v>
       </c>
       <c r="M100">
-        <v>353.2350024</v>
+        <v>356.8394412</v>
       </c>
       <c r="N100">
-        <v>-311.6350024</v>
+        <v>-315.2394412</v>
       </c>
       <c r="O100">
-        <v>-82.583275636</v>
+        <v>-83.53845191800001</v>
       </c>
       <c r="P100">
-        <v>-229.051726764</v>
+        <v>-231.700989282</v>
       </c>
       <c r="Q100">
-        <v>-149.851726764</v>
+        <v>-152.500989282</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.045934785599438</v>
+        <v>4.046069571198876</v>
       </c>
       <c r="T100">
-        <v>46.19248927481381</v>
+        <v>92.38497854962763</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03120868522399863</v>
+        <v>0.03089344597931178</v>
       </c>
       <c r="W100">
-        <v>0.2284409920241811</v>
+        <v>0.2285153254380783</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1177686234867873</v>
+        <v>0.1165790414313651</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2666908678956863</v>
-      </c>
-      <c r="C101">
-        <v>-1131.979962684703</v>
-      </c>
-      <c r="D101">
-        <v>288.7340373152973</v>
-      </c>
-      <c r="E101">
-        <v>1206.514</v>
-      </c>
-      <c r="F101">
-        <v>1513.314</v>
-      </c>
-      <c r="G101">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="H101">
-        <v>1221.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>120.8</v>
-      </c>
-      <c r="K101">
-        <v>79.2</v>
-      </c>
-      <c r="L101">
-        <v>41.59999999999999</v>
-      </c>
-      <c r="M101">
-        <v>356.8394412</v>
-      </c>
-      <c r="N101">
-        <v>-315.2394412</v>
-      </c>
-      <c r="O101">
-        <v>-83.53845191800001</v>
-      </c>
-      <c r="P101">
-        <v>-231.700989282</v>
-      </c>
-      <c r="Q101">
-        <v>-152.500989282</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.046069571198876</v>
-      </c>
-      <c r="T101">
-        <v>92.38497854962763</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03089344597931178</v>
-      </c>
-      <c r="W101">
-        <v>0.2285153254380783</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1165790414313651</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
